--- a/output/Matched_orders.xlsx
+++ b/output/Matched_orders.xlsx
@@ -67,7 +67,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -103,30 +103,6 @@
       <left style="thin"/>
       <right/>
       <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top/>
       <bottom style="thin"/>
     </border>
     <border>
@@ -151,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -175,18 +151,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -560,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -601,7 +565,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    N476493</t>
+          <t xml:space="preserve">    N465376</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -611,7 +575,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>CH332</t>
+          <t>KTNMINI</t>
         </is>
       </c>
       <c r="B4" s="8" t="n">
@@ -619,200 +583,19 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Champion CH332 Clarinet Pull-Through Cleaning Tool</t>
+          <t>BOSS KATANA-MINI Portable Battery Guitar Amplifier - Compact Tone with Onboard Effects</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>all on po | 01/03/2026 11:35: RCB1020 ON PO - 01/03/2026 11:35 | RCB1020  IN WAITING AREA | 01/03/2026 11:35: RCB1020 ON PO - 01/03/2026 11:35 | Messaged customer about delay. Asked to wait. ETA: March 6th (Friday). Items: Faxx Large Mouthpiece Cushion in Black (PK-2) | Customer confirmed happy to wait for order. Message: Hi Kyal,  Thats fine. Thanks for letting me know.  Kind regards, Stephanie  On Tue, 3 Mar 2026, 5:11 pm Scarlett Music, &lt;kyal@mail.scarlettmusic.c... | ch332 &amp;rcb1020 in waiting area | WFMCBL set aside, just waiting on WB205</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>RCB1020</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Rico Royal Bb Clarinet Reeds, Strength 2.0, 10-pack</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>WB205</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Herco WB205 Clarinet Thumb Rest Cushions</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>*WFMCBL</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Faxx Large Mouthpiece Cushion in Black (PK-2)</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    N476655</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>8400125AUSTRALIS</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Gibson Truss Rod Cover Blank (Black)</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>MN105 on po | Messaged customer about delay. Asked to wait. ETA: March 9th (Monday). Items: Music Nomad MN105 Fretboard F-one Oil Cleaner &amp; Conditioner - 60ml | truss rod cover on PO, MN105 set aside</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>*MN105</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Music Nomad MN105 Fretboard F-one Oil Cleaner &amp; Conditioner - 60ml</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    N476670</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>*PR2014</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Protection Racket Proline Floor Tom Case (14" x 14")</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>PR2014 ON PO | Messaged customer about delay. Asked to wait. ETA: March 9th (Monday). Items: Protection Racket Proline Floor Tom Case (14" x 14") | Customer confirmed happy to wait for order. Message: Yes mate that's fine to wait for stock. Thanks for letting me know  On Wed, 4 Mar 2026, 18:16 Scarlett Music, &lt;kyal@mail.scarlettmusic.com.au&gt; wrot... | PR501210 on PO, PR2014 set aside</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>PR501210</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Protection Racket Proline Egg Shape Tom Case (12" x 8")</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    07-14326-09522</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="6" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>*MN106</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Music Nomad MN106 Tune-It Lubricant - 10ml</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>Satchel.</t>
+          <t>Checking ETA with Roland | Due late Jan, Messaged about waiting - Kyal | Happy to wait, Dropship organised, awaiting tracking - Kyal</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A18:D18"/>
+  <mergeCells count="2">
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -825,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -875,277 +658,33 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>N476493</t>
-        </is>
-      </c>
-      <c r="C2" s="15" t="inlineStr">
-        <is>
-          <t>CH332</t>
-        </is>
-      </c>
-      <c r="D2" s="16" t="inlineStr">
-        <is>
-          <t>Champion CH332 Clarinet Pull-Through Cleaning Tool</t>
-        </is>
-      </c>
-      <c r="E2" s="15" t="inlineStr"/>
-      <c r="F2" s="15" t="n">
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>N465376</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>KTNMINI</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>BOSS KATANA-MINI Portable Battery Guitar Amplifier - Compact Tone with Onboard Effects</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr"/>
+      <c r="F2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="16" t="inlineStr">
-        <is>
-          <t>all on po | 01/03/2026 11:35: RCB1020 ON PO - 01/03/2026 11:35 | RCB1020  IN WAITING AREA | 01/03/2026 11:35: RCB1020 ON PO - 01/03/2026 11:35 | Messaged customer about delay. Asked to wait. ETA: March 6th (Friday). Items: Faxx Large Mouthpiece Cushion in Black (PK-2) | Customer confirmed happy to wait for order. Message: Hi Kyal,  Thats fine. Thanks for letting me know.  Kind regards, Stephanie  On Tue, 3 Mar 2026, 5:11 pm Scarlett Music, &lt;kyal@mail.scarlettmusic.c... | ch332 &amp;rcb1020 in waiting area | WFMCBL set aside, just waiting on WB205</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>N476493</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>RCB1020</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>Rico Royal Bb Clarinet Reeds, Strength 2.0, 10-pack</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr"/>
-      <c r="F3" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="16" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>N476493</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>WB205</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>Herco WB205 Clarinet Thumb Rest Cushions</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr"/>
-      <c r="F4" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="16" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>N476493</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>*WFMCBL</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>Faxx Large Mouthpiece Cushion in Black (PK-2)</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="16" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>N476655</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>8400125AUSTRALIS</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Gibson Truss Rod Cover Blank (Black)</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr"/>
-      <c r="F7" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>MN105 on po | Messaged customer about delay. Asked to wait. ETA: March 9th (Monday). Items: Music Nomad MN105 Fretboard F-one Oil Cleaner &amp; Conditioner - 60ml | truss rod cover on PO, MN105 set aside</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>N476655</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>*MN105</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Music Nomad MN105 Fretboard F-one Oil Cleaner &amp; Conditioner - 60ml</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="16" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>N476670</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>*PR2014</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>Protection Racket Proline Floor Tom Case (14" x 14")</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>PR2014 ON PO | Messaged customer about delay. Asked to wait. ETA: March 9th (Monday). Items: Protection Racket Proline Floor Tom Case (14" x 14") | Customer confirmed happy to wait for order. Message: Yes mate that's fine to wait for stock. Thanks for letting me know  On Wed, 4 Mar 2026, 18:16 Scarlett Music, &lt;kyal@mail.scarlettmusic.com.au&gt; wrot... | PR501210 on PO, PR2014 set aside</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>N476670</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>PR501210</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>Protection Racket Proline Egg Shape Tom Case (12" x 8")</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr"/>
-      <c r="F11" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="16" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>eBay</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>07-14326-09522</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>*MN106</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>Music Nomad MN106 Tune-It Lubricant - 10ml</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>Satchel.</t>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>Checking ETA with Roland | Due late Jan, Messaged about waiting - Kyal | Happy to wait, Dropship organised, awaiting tracking - Kyal</t>
         </is>
       </c>
     </row>

--- a/output/Matched_orders.xlsx
+++ b/output/Matched_orders.xlsx
@@ -67,7 +67,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -123,11 +123,35 @@
       <top/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -151,6 +175,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -524,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -565,7 +601,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    N465376</t>
+          <t xml:space="preserve">    N476665</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -575,7 +611,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>KTNMINI</t>
+          <t>*50982PT</t>
         </is>
       </c>
       <c r="B4" s="8" t="n">
@@ -583,19 +619,3814 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>BOSS KATANA-MINI Portable Battery Guitar Amplifier - Compact Tone with Onboard Effects</t>
+          <t>Violin Chinrest-Wittner Spaceage 1/2-1/4</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Checking ETA with Roland | Due late Jan, Messaged about waiting - Kyal | Happy to wait, Dropship organised, awaiting tracking - Kyal</t>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476828</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>*35088PT</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Basso Floral Leather Guitar Strap - Whiskey, 7.5cm Width, Adjustable Length 1.00-1.45m, Foam Lining, Reinforced Ends</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476877</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>*10857PT</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Aquila ThunderBlack 140U Bass Ukulele Set</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476893</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>*DA570</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Xtreme Drum Hardware Bag Extra Heavy Duty Padded Bag 100Cm x 35Cm x 35Cm</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476901</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>*MNCC-15L-SOPJD</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Martinez 'Natural Series' Left Handed Spruce Top Acoustic-Electric Classical Cutaway Guitar (Open Pore)</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476909</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>*LP008CS</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>LP Chad Smith Signature Ridge Rider Cowbell</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476916</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>*EDA30B</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Carlsbro EDA30B Electronic Drum Amplifier w/ Bluetooth</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476919</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>*606101AUSTRALIS</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Armour CYB250X Cymbal Bag</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>both on po | 606101AUSTRALIS in waiting area</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>PR9025</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Protection Racket 15" Fleece Drum Throne Seat Cover</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476924</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>*G30P1</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Gotoh G30 Acoustic Machine Heads 3-a-Side Chrome with White Buttons</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476927</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>*S14H30</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Evans Clear 300 Snare Side Drum Head, 14 Inch *SKIN ONLY*</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476934</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>114FLJ3-24</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>24 x Jim Dunlop Tortex Jazz III FLEX 1.14MM Gauge Guitar Picks 468R *NEW*</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>114FLJ3 and NYNW072 on PO, NYXL1156 set aside</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>NYNW072</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>D'Addario NYXL Nickel Wound Electric Guitar Single String, .072</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>*NYXL1156</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>D'Addario NYXL1156 Nickel Wound Electric Guitar Strings, Medium Top - Extra-Heavy Bottom, 11-56</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476940</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>*TGB-B-BLKJD</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Tiki Deluxe Baritone Ukulele Bag (Black)</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476942</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>*MP-SJ34T-TGRJD</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Martinez 'Slim Jim' 3/4 Size Student Classical Guitar Pack with Built In Tuner (Teal Green)</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476958</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>*ED418</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>AMS 02 Inch Hum A Zoo Kazoo - ED418</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>GSC42446</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Gibraltar Standard Drum Key on Tear-off Card Display - Pk 6</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476966</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>*ECB84</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>D'Addario ECB84 Chromes Bass Guitar Strings, Custom Light, 40-100, Long Scale</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476983</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>*MA410B</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Xtreme Microphone Short Boom Stand MA410B</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476990</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>*MZ-BT2-KOAJD</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Martinez Acoustic Babe Traveller Guitar (Koa)</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476996</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="6" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>1001133240</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>Essential Music Theory Grs 4-6 Answer Book (Softcover Book)</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>PW-VG-01
+and cm20red on po | Books sent Encore Aus Post Express</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>ALF17234</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>Essentials Of Music Theory Complete Books 1-3 (Softcover Book)</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>CM20RED</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>Cherry Metronome with Metal Mechanism &amp; Bell in Red Plastic Casing</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>*PW-VG-01</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Planet Waves Varigrip Adjustable Hand Exerciser</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr"/>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476997</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="n"/>
+      <c r="C64" s="5" t="n"/>
+      <c r="D64" s="6" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>*GDVP4</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>JIM DUNLOP Mini Volume x Guitar Effects Pedal *NEW* Black GDVP4</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>GDVP4 on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>SN-DC65</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Strymon DC Power Cables 36inch Straight to Right Angle - 5 Pack</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477003</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="6" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>*CP379</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>LP CP Wood Head Sng Row 10 Inch Tambourine</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>on po | centre open mon-fri 9.30am-5pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477006</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="6" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>*DA789</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>1 x CPK DA789 Retractable Wire Drum Brushes Black Rubber Handle</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>Brushes on PO, metronome set aside</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>WMT230WH</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Cherub Rechargeable Digital Metronome &amp; Tuner in White</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr"/>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477010</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="n"/>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>*HT-AMPERO-II</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Hotone Ampero II Multi Effects Modelling Pedal</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477013</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="n"/>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>*CX-0114-10</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>Remo 14" Control Sound X Coated Drum Head</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477033</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="n"/>
+      <c r="C81" s="5" t="n"/>
+      <c r="D81" s="6" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>*DA577PR</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>Xtreme DA577PR Rock Size Drum Bag Set</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477036</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="n"/>
+      <c r="C84" s="5" t="n"/>
+      <c r="D84" s="6" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>*TDH251</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>Mano Percussion 9/10 Inch Mini Conga Head Set Natural Hide Pair</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>ON PO | Please call me upon delivery.thankyou  0490928281</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477038</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="n"/>
+      <c r="C87" s="5" t="n"/>
+      <c r="D87" s="6" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>*MMR5W</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>Mini Multi Instrument Rack Stand with Wheels</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477040</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="n"/>
+      <c r="C90" s="5" t="n"/>
+      <c r="D90" s="6" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t>*BU60</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" s="13" t="inlineStr">
+        <is>
+          <t>3 x Mahalo Ukulele Felt Picks 3.2mm Flat Soft Tone  Hawaiian Pack Uke</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>Both on PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>MJ1TBR</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>Mahalo J Series Soprano Ukulele Trans Brown MJ1TBR with Gig Bag</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr"/>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477041</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="5" t="n"/>
+      <c r="D94" s="6" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>*CDSP041</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>Carlsbro CSD35M Hi-Hat Pack</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477042</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="n"/>
+      <c r="C97" s="5" t="n"/>
+      <c r="D97" s="6" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>*JPJLFJ</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>JIM DUNLOP Black Jeff Loomis Custom Flow Jumbo Guitar Pick Player's Pack.</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477072</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="n"/>
+      <c r="C100" s="5" t="n"/>
+      <c r="D100" s="6" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>*XRC2U</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>Xtreme 2U Rack Mount Road Case</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>on po | Leave at front door if no one home</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477074</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="5" t="n"/>
+      <c r="D103" s="6" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>*VC204TWR</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>Valencia Series 200 Classical Guitar (Transparent Wine Red)</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477085</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="n"/>
+      <c r="C106" s="5" t="n"/>
+      <c r="D106" s="6" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>*UE863</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>1st Note Kazoo UE863 Assorted Colors (Single Kazoo)</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477113</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="n"/>
+      <c r="C109" s="5" t="n"/>
+      <c r="D109" s="6" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>*22544PT</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>Conductor Baton-Ebony Handle 18in</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>ON PO | Dropship organised, awaiting tracking - Kyal</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477126</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="n"/>
+      <c r="C112" s="5" t="n"/>
+      <c r="D112" s="6" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>*XSAPB1356</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>D'Addario XS Coated Acoustic Phosphor Bronze Strings - Medium Set (13-56)</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477127</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="n"/>
+      <c r="C115" s="5" t="n"/>
+      <c r="D115" s="6" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>*SO-10</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" s="13" t="inlineStr">
+        <is>
+          <t>SoundOff by Evans Drum Mute, 10 Inch</t>
+        </is>
+      </c>
+      <c r="D116" s="14" t="inlineStr">
+        <is>
+          <t>SO-8 ON PO. Others set aside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>SO-12</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" s="13" t="inlineStr">
+        <is>
+          <t>SoundOff by Evans Drum Mute, 12 Inch</t>
+        </is>
+      </c>
+      <c r="D117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>SO-13</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" s="13" t="inlineStr">
+        <is>
+          <t>SoundOff by Evans Drum Mute, 13 Inch</t>
+        </is>
+      </c>
+      <c r="D118" s="14" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>*SO-8</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>SoundOff by Evans Drum Mute, 8 Inch</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr"/>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477128</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="n"/>
+      <c r="C121" s="5" t="n"/>
+      <c r="D121" s="6" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>*SOMS-MS2-BLKJD</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>SoundArt Orchestral Music Stand (Black)</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: SOMS-MS2-BLK ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477132</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="n"/>
+      <c r="C124" s="5" t="n"/>
+      <c r="D124" s="6" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>*MSD17</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>Platinum Extension Music Stand Attaches To Mic Stand Three Postion Black</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: MSD17 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477146</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="n"/>
+      <c r="C127" s="5" t="n"/>
+      <c r="D127" s="6" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>*LP281</t>
+        </is>
+      </c>
+      <c r="B128" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>LP Professional Maracas</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: LP281 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477157</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="n"/>
+      <c r="C130" s="5" t="n"/>
+      <c r="D130" s="6" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>*HC3065</t>
+        </is>
+      </c>
+      <c r="B131" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>Xtreme HC3065 Parlour Size Acoustic Guitar Case - Black</t>
+        </is>
+      </c>
+      <c r="D131" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477193</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="n"/>
+      <c r="C133" s="5" t="n"/>
+      <c r="D133" s="6" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>*MPC24FS</t>
+        </is>
+      </c>
+      <c r="B134" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>Mano 8 inch Tuneable Djembe - Forest Spirit Finish</t>
+        </is>
+      </c>
+      <c r="D134" s="10" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: MPC24FS ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477203</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="n"/>
+      <c r="C136" s="5" t="n"/>
+      <c r="D136" s="6" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>BVMRK72-08-2PCMC</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" s="13" t="inlineStr">
+        <is>
+          <t>Boveda Humidity Control 2 pc Size 8,  72% For Single &amp;  Double Reed Storage</t>
+        </is>
+      </c>
+      <c r="D137" s="14" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: BVMRK72-08-2P, CH331, RCB1015, WSCORK ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>CH331</t>
+        </is>
+      </c>
+      <c r="B138" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" s="13" t="inlineStr">
+        <is>
+          <t>Champion CH331 Soprano Saxophone and Clarinet Pull-Through Cleaner</t>
+        </is>
+      </c>
+      <c r="D138" s="14" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>MS105</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" s="13" t="inlineStr">
+        <is>
+          <t>Xtreme Music Stand Tripod Base w/bag</t>
+        </is>
+      </c>
+      <c r="D139" s="14" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>*RCB1015</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" s="13" t="inlineStr">
+        <is>
+          <t>Rico Royal Bb Clarinet Reeds, Strength 1.5, 10-pack</t>
+        </is>
+      </c>
+      <c r="D140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>WSCORK</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>Superslick Cork Grease Lipstick Style Dispenser</t>
+        </is>
+      </c>
+      <c r="D141" s="10" t="inlineStr"/>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477215</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="n"/>
+      <c r="C143" s="5" t="n"/>
+      <c r="D143" s="6" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>*RMP01B</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>Reserve Mouthpiece Patch, Black, 5 pack</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: RMP01B ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477247</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="n"/>
+      <c r="C146" s="5" t="n"/>
+      <c r="D146" s="6" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>*EDP002</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>DXP 32-Note Chromatic Glockenspiel, F5 - C8 with Nylon Beaters and Rack</t>
+        </is>
+      </c>
+      <c r="D147" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477249</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="n"/>
+      <c r="C149" s="5" t="n"/>
+      <c r="D149" s="6" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t>*DA581</t>
+        </is>
+      </c>
+      <c r="B150" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>22" Cymbal Bag</t>
+        </is>
+      </c>
+      <c r="D150" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477267</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="n"/>
+      <c r="C152" s="5" t="n"/>
+      <c r="D152" s="6" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>*J27H04</t>
+        </is>
+      </c>
+      <c r="B153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>D'Addario J27H04  Student Nylon Classical Guitar Single String, Hard Tension, Fourth String</t>
+        </is>
+      </c>
+      <c r="D153" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477271</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="n"/>
+      <c r="C155" s="5" t="n"/>
+      <c r="D155" s="6" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t>*108495PT</t>
+        </is>
+      </c>
+      <c r="B156" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" s="13" t="inlineStr">
+        <is>
+          <t>Aquila Super Nylgut Baritone Ukulele String Set - Low D Tuning 128U</t>
+        </is>
+      </c>
+      <c r="D156" s="14" t="inlineStr">
+        <is>
+          <t>ej88b
+108495 both on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>AQ129U</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" s="13" t="inlineStr">
+        <is>
+          <t>Aquila Super Nylgut High-G Baritone Ukulele Strings Set</t>
+        </is>
+      </c>
+      <c r="D157" s="14" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t>*EJ88B</t>
+        </is>
+      </c>
+      <c r="B158" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" s="9" t="inlineStr">
+        <is>
+          <t>D'Addario EJ88B Nyltech Ukulele Strings, Baritone</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="inlineStr"/>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477274</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="n"/>
+      <c r="C160" s="5" t="n"/>
+      <c r="D160" s="6" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="7" t="inlineStr">
+        <is>
+          <t>*EJ26-10P</t>
+        </is>
+      </c>
+      <c r="B161" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C161" s="9" t="inlineStr">
+        <is>
+          <t>D'Addario EJ26-10P Phosphor Bronze Acoustic Guitar Strings, Custom Light, 11-52, 10 Sets</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477299</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="n"/>
+      <c r="C163" s="5" t="n"/>
+      <c r="D163" s="6" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="inlineStr">
+        <is>
+          <t>*RJA1025</t>
+        </is>
+      </c>
+      <c r="B164" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>Rico Alto Sax Reeds, Strength 2.5, 10-pack</t>
+        </is>
+      </c>
+      <c r="D164" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477315</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="n"/>
+      <c r="C166" s="5" t="n"/>
+      <c r="D166" s="6" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="7" t="inlineStr">
+        <is>
+          <t>*UE806</t>
+        </is>
+      </c>
+      <c r="B167" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C167" s="9" t="inlineStr">
+        <is>
+          <t>Mano Percussion 8 Note Coloured Xylo C6-C7 Solid Wood</t>
+        </is>
+      </c>
+      <c r="D167" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="18" customHeight="1">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477329</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="n"/>
+      <c r="C169" s="5" t="n"/>
+      <c r="D169" s="6" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="7" t="inlineStr">
+        <is>
+          <t>*DD2200JPS</t>
+        </is>
+      </c>
+      <c r="B170" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>Dimarzio John Petrucci Cliplock Guitar Strap Adjustable 35"-51</t>
+        </is>
+      </c>
+      <c r="D170" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="18" customHeight="1">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477336</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="n"/>
+      <c r="C172" s="5" t="n"/>
+      <c r="D172" s="6" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>*J5006PK</t>
+        </is>
+      </c>
+      <c r="B173" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C173" s="13" t="inlineStr">
+        <is>
+          <t>Jim Dunlop Ergo Pick Holder</t>
+        </is>
+      </c>
+      <c r="D173" s="14" t="inlineStr">
+        <is>
+          <t>both on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="7" t="inlineStr">
+        <is>
+          <t>J7007</t>
+        </is>
+      </c>
+      <c r="B174" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>Dunlop Ergonomic Guitar Pick Shaped Strap Lock</t>
+        </is>
+      </c>
+      <c r="D174" s="10" t="inlineStr"/>
+    </row>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AMAZON AU</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="18" customHeight="1">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476962</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="n"/>
+      <c r="C177" s="5" t="n"/>
+      <c r="D177" s="6" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="11" t="inlineStr">
+        <is>
+          <t>RIA0315</t>
+        </is>
+      </c>
+      <c r="B178" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C178" s="13" t="inlineStr">
+        <is>
+          <t>Rico Soprano Sax Reeds, Strength 1.5, 3-pack</t>
+        </is>
+      </c>
+      <c r="D178" s="14" t="inlineStr">
+        <is>
+          <t>Reeds set aside, mouthpiece on PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t>*RRGMPCSSXB3</t>
+        </is>
+      </c>
+      <c r="B179" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C179" s="9" t="inlineStr">
+        <is>
+          <t>Rico Graftonite Soprano Sax Mouthpiece, B3</t>
+        </is>
+      </c>
+      <c r="D179" s="10" t="inlineStr"/>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477290</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="n"/>
+      <c r="C181" s="5" t="n"/>
+      <c r="D181" s="6" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t>*J3004</t>
+        </is>
+      </c>
+      <c r="B182" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" s="9" t="inlineStr">
+        <is>
+          <t>D'Addario J3004 Rectified Classical Guitar Single String, Normal Tension, Fourth String</t>
+        </is>
+      </c>
+      <c r="D182" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="20" customHeight="1">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BIGW</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="18" customHeight="1">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476886</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="n"/>
+      <c r="C185" s="5" t="n"/>
+      <c r="D185" s="6" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="7" t="inlineStr">
+        <is>
+          <t>*28470PT</t>
+        </is>
+      </c>
+      <c r="B186" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C186" s="9" t="inlineStr">
+        <is>
+          <t>Violin Bridge Aubert France 5 Prepared 4/4</t>
+        </is>
+      </c>
+      <c r="D186" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="18" customHeight="1">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476929</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="n"/>
+      <c r="C188" s="5" t="n"/>
+      <c r="D188" s="6" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="7" t="inlineStr">
+        <is>
+          <t>*ROK20BL</t>
+        </is>
+      </c>
+      <c r="B189" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C189" s="9" t="inlineStr">
+        <is>
+          <t>Carson Cable Co Rocklines 20ft Braided Blue Guitar Cable with Straight Jacks</t>
+        </is>
+      </c>
+      <c r="D189" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="18" customHeight="1">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476945</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="n"/>
+      <c r="C191" s="5" t="n"/>
+      <c r="D191" s="6" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="7" t="inlineStr">
+        <is>
+          <t>*D137A</t>
+        </is>
+      </c>
+      <c r="B192" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C192" s="9" t="inlineStr">
+        <is>
+          <t>DXP 7A OAK Wood Tip Drum Sticks</t>
+        </is>
+      </c>
+      <c r="D192" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="18" customHeight="1">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476975</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="n"/>
+      <c r="C194" s="5" t="n"/>
+      <c r="D194" s="6" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="7" t="inlineStr">
+        <is>
+          <t>*ROK20SS</t>
+        </is>
+      </c>
+      <c r="B195" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C195" s="9" t="inlineStr">
+        <is>
+          <t>Carson Cable Co Rocklines 20ft Noiseless Guitar Cable with Straight Jacks</t>
+        </is>
+      </c>
+      <c r="D195" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="18" customHeight="1">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477166</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="n"/>
+      <c r="C197" s="5" t="n"/>
+      <c r="D197" s="6" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="7" t="inlineStr">
+        <is>
+          <t>*JPP315</t>
+        </is>
+      </c>
+      <c r="B198" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C198" s="9" t="inlineStr">
+        <is>
+          <t>Dunlop 1.5mm Primetone Standard Guitar Picks with Grip Players Pack</t>
+        </is>
+      </c>
+      <c r="D198" s="10" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: JPP315 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="18" customHeight="1">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477222</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="n"/>
+      <c r="C200" s="5" t="n"/>
+      <c r="D200" s="6" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="7" t="inlineStr">
+        <is>
+          <t>*HC298</t>
+        </is>
+      </c>
+      <c r="B201" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C201" s="9" t="inlineStr">
+        <is>
+          <t>CNB V-CASE Shaped Banjo Case with Black Vinyl and Orange Stitching</t>
+        </is>
+      </c>
+      <c r="D201" s="10" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:43: HC298 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="18" customHeight="1">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477258</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="n"/>
+      <c r="C203" s="5" t="n"/>
+      <c r="D203" s="6" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="7" t="inlineStr">
+        <is>
+          <t>*MA409</t>
+        </is>
+      </c>
+      <c r="B204" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C204" s="9" t="inlineStr">
+        <is>
+          <t>AMS MA409 Heavy Duty Mic Boom Stand with 80cm Boom Arm, Chrome Finish</t>
+        </is>
+      </c>
+      <c r="D204" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="18" customHeight="1">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477291</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="n"/>
+      <c r="C206" s="5" t="n"/>
+      <c r="D206" s="6" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="7" t="inlineStr">
+        <is>
+          <t>*CHST-65JD</t>
+        </is>
+      </c>
+      <c r="B207" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C207" s="9" t="inlineStr">
+        <is>
+          <t>Crossfire Clip-On Headstock Tuner for Guitar  Bass  Ukulele &amp; Violin</t>
+        </is>
+      </c>
+      <c r="D207" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="18" customHeight="1">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477330</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="n"/>
+      <c r="C209" s="5" t="n"/>
+      <c r="D209" s="6" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="7" t="inlineStr">
+        <is>
+          <t>*UE848R</t>
+        </is>
+      </c>
+      <c r="B210" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" s="9" t="inlineStr">
+        <is>
+          <t>Mano 8 Inch Hand Drum Red with Wooden Shell and Mallet Included</t>
+        </is>
+      </c>
+      <c r="D210" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="20" customHeight="1">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EVERYDAYMARKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="18" customHeight="1">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476819</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="n"/>
+      <c r="C213" s="5" t="n"/>
+      <c r="D213" s="6" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="7" t="inlineStr">
+        <is>
+          <t>*UE862</t>
+        </is>
+      </c>
+      <c r="B214" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C214" s="9" t="inlineStr">
+        <is>
+          <t>Mano Percussion MP Percussion Pack - 8-Piece Set with Carry Bag</t>
+        </is>
+      </c>
+      <c r="D214" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="18" customHeight="1">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477195</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="n"/>
+      <c r="C216" s="5" t="n"/>
+      <c r="D216" s="6" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="7" t="inlineStr">
+        <is>
+          <t>*KOR3</t>
+        </is>
+      </c>
+      <c r="B217" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C217" s="9" t="inlineStr">
+        <is>
+          <t>Kwikfret Orange Oil 100ml Fretboard Cleaner and Protector</t>
+        </is>
+      </c>
+      <c r="D217" s="10" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: KOR3 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="18" customHeight="1">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477218</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="n"/>
+      <c r="C219" s="5" t="n"/>
+      <c r="D219" s="6" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="7" t="inlineStr">
+        <is>
+          <t>*KOR3</t>
+        </is>
+      </c>
+      <c r="B220" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C220" s="9" t="inlineStr">
+        <is>
+          <t>Kwikfret Orange Oil 100ml Fretboard Cleaner and Protector</t>
+        </is>
+      </c>
+      <c r="D220" s="10" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: KOR3 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="20" customHeight="1">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  KOGAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="18" customHeight="1">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476826</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="n"/>
+      <c r="C223" s="5" t="n"/>
+      <c r="D223" s="6" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="7" t="inlineStr">
+        <is>
+          <t>*71816PT</t>
+        </is>
+      </c>
+      <c r="B224" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C224" s="9" t="inlineStr">
+        <is>
+          <t>Pickboy Nylon Pro Guitar Picks - 12 Pack, 0.70mm, Made in Japan</t>
+        </is>
+      </c>
+      <c r="D224" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="18" customHeight="1">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N476913</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="n"/>
+      <c r="C226" s="5" t="n"/>
+      <c r="D226" s="6" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="7" t="inlineStr">
+        <is>
+          <t>*1408107638</t>
+        </is>
+      </c>
+      <c r="B227" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C227" s="9" t="inlineStr">
+        <is>
+          <t>Abracadabra Saxophone Book Only 3rd Ed (Softcover Book)</t>
+        </is>
+      </c>
+      <c r="D227" s="10" t="inlineStr">
+        <is>
+          <t>Dropship organised, awaiting tracking - Kyal</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="18" customHeight="1">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477025</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="n"/>
+      <c r="C229" s="5" t="n"/>
+      <c r="D229" s="6" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="7" t="inlineStr">
+        <is>
+          <t>*VC103BUS</t>
+        </is>
+      </c>
+      <c r="B230" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C230" s="9" t="inlineStr">
+        <is>
+          <t>Valencia 3/4 Size Nylon String Student Guitar Blue</t>
+        </is>
+      </c>
+      <c r="D230" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="18" customHeight="1">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477050</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="n"/>
+      <c r="C232" s="5" t="n"/>
+      <c r="D232" s="6" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="7" t="inlineStr">
+        <is>
+          <t>*DSC316</t>
+        </is>
+      </c>
+      <c r="B233" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C233" s="9" t="inlineStr">
+        <is>
+          <t>DXP 16 Inch Crash Cymbal - Alloy</t>
+        </is>
+      </c>
+      <c r="D233" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="18" customHeight="1">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477051</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="n"/>
+      <c r="C235" s="5" t="n"/>
+      <c r="D235" s="6" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="11" t="inlineStr">
+        <is>
+          <t>1CAB4-15BT2</t>
+        </is>
+      </c>
+      <c r="B236" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C236" s="13" t="inlineStr">
+        <is>
+          <t>Planet Waves Beatles Signature Guitar Pick Tins, Stripes</t>
+        </is>
+      </c>
+      <c r="D236" s="14" t="inlineStr">
+        <is>
+          <t>all on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="11" t="inlineStr">
+        <is>
+          <t>*RN10</t>
+        </is>
+      </c>
+      <c r="B237" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C237" s="13" t="inlineStr">
+        <is>
+          <t>Danelectro Honeytone Mini Amp Burgundy Battery Powered</t>
+        </is>
+      </c>
+      <c r="D237" s="14" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="11" t="inlineStr">
+        <is>
+          <t>*RN10A</t>
+        </is>
+      </c>
+      <c r="B238" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C238" s="13" t="inlineStr">
+        <is>
+          <t>Danelectro Honeytone Mini Amplifier Aqua</t>
+        </is>
+      </c>
+      <c r="D238" s="14" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="7" t="inlineStr">
+        <is>
+          <t>*RN10B</t>
+        </is>
+      </c>
+      <c r="B239" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C239" s="9" t="inlineStr">
+        <is>
+          <t>Danelectro Honeytone Mini Amp Battery Powered - RN10 Series</t>
+        </is>
+      </c>
+      <c r="D239" s="10" t="inlineStr"/>
+    </row>
+    <row r="241" ht="18" customHeight="1">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477053</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="n"/>
+      <c r="C241" s="5" t="n"/>
+      <c r="D241" s="6" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="7" t="inlineStr">
+        <is>
+          <t>*UE776</t>
+        </is>
+      </c>
+      <c r="B242" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C242" s="9" t="inlineStr">
+        <is>
+          <t>Mano Percussion 10 Inch Tunable Tambour with 8 Lugs</t>
+        </is>
+      </c>
+      <c r="D242" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="18" customHeight="1">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477060</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="n"/>
+      <c r="C244" s="5" t="n"/>
+      <c r="D244" s="6" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="11" t="inlineStr">
+        <is>
+          <t>*MINI-PSU</t>
+        </is>
+      </c>
+      <c r="B245" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C245" s="13" t="inlineStr">
+        <is>
+          <t>Laney Power Supply for Mini Amps - 12V DC 2A</t>
+        </is>
+      </c>
+      <c r="D245" s="14" t="inlineStr">
+        <is>
+          <t>both on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="7" t="inlineStr">
+        <is>
+          <t>*MINISTACK-B-LION</t>
+        </is>
+      </c>
+      <c r="B246" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C246" s="9" t="inlineStr">
+        <is>
+          <t>Laney Lionheart Ministack Bluetooth Guitar Amplifier</t>
+        </is>
+      </c>
+      <c r="D246" s="10" t="inlineStr"/>
+    </row>
+    <row r="248" ht="18" customHeight="1">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477134</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="n"/>
+      <c r="C248" s="5" t="n"/>
+      <c r="D248" s="6" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="7" t="inlineStr">
+        <is>
+          <t>*CDSP035</t>
+        </is>
+      </c>
+      <c r="B249" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C249" s="9" t="inlineStr">
+        <is>
+          <t>Carlsbro CSD25M Cable Loom for CSD25M, CSD35M1, CSD45M Models</t>
+        </is>
+      </c>
+      <c r="D249" s="10" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: CDSP035 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="18" customHeight="1">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477173</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="n"/>
+      <c r="C251" s="5" t="n"/>
+      <c r="D251" s="6" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="7" t="inlineStr">
+        <is>
+          <t>*1408107638</t>
+        </is>
+      </c>
+      <c r="B252" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C252" s="9" t="inlineStr">
+        <is>
+          <t>Abracadabra Saxophone Book Only 3rd Ed (Softcover Book)</t>
+        </is>
+      </c>
+      <c r="D252" s="10" t="inlineStr">
+        <is>
+          <t>Dropship organised, awaiting tracking - Kyal</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="18" customHeight="1">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    N477236</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="n"/>
+      <c r="C254" s="5" t="n"/>
+      <c r="D254" s="6" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="7" t="inlineStr">
+        <is>
+          <t>*MA367</t>
+        </is>
+      </c>
+      <c r="B255" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C255" s="9" t="inlineStr">
+        <is>
+          <t>AMS Mic Stand Chrome</t>
+        </is>
+      </c>
+      <c r="D255" s="10" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:43: MA367 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="20" customHeight="1">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EBAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="18" customHeight="1">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    01-14338-85679</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="n"/>
+      <c r="C258" s="5" t="n"/>
+      <c r="D258" s="6" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="7" t="inlineStr">
+        <is>
+          <t>*MEP-12V2AJD</t>
+        </is>
+      </c>
+      <c r="B259" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C259" s="9" t="inlineStr">
+        <is>
+          <t>Mooer 12 Volt DC 2 Amp Effects Pedal Power Supply</t>
+        </is>
+      </c>
+      <c r="D259" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="18" customHeight="1">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    03-14227-69047</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="n"/>
+      <c r="C261" s="5" t="n"/>
+      <c r="D261" s="6" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="11" t="inlineStr">
+        <is>
+          <t>*EDA30B</t>
+        </is>
+      </c>
+      <c r="B262" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C262" s="13" t="inlineStr">
+        <is>
+          <t>Carlsbro EDA30B Electronic Drum Amplifier w/ Bluetooth</t>
+        </is>
+      </c>
+      <c r="D262" s="14" t="inlineStr">
+        <is>
+          <t>in collect area, customer contacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="7" t="inlineStr">
+        <is>
+          <t>71MG50GFXEF</t>
+        </is>
+      </c>
+      <c r="B263" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C263" s="9" t="inlineStr">
+        <is>
+          <t>Marshall MG50GFX: 50W MG Gold Combo</t>
+        </is>
+      </c>
+      <c r="D263" s="10" t="inlineStr">
+        <is>
+          <t>in collect area, customer contacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="18" customHeight="1">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    04-14343-35529</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="n"/>
+      <c r="C265" s="5" t="n"/>
+      <c r="D265" s="6" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="11" t="inlineStr">
+        <is>
+          <t>*JPTJH3</t>
+        </is>
+      </c>
+      <c r="B266" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C266" s="13" t="inlineStr">
+        <is>
+          <t>Jim Dunlop Tortex Jazz H3 Player Pack Guitar Picks 1.14 mm</t>
+        </is>
+      </c>
+      <c r="D266" s="14" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="7" t="inlineStr">
+        <is>
+          <t>PL015-10</t>
+        </is>
+      </c>
+      <c r="B267" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C267" s="9" t="inlineStr">
+        <is>
+          <t>10 x D'Addario PL015 Single Plain Steel .015 Acoustic or Electric Guitar Strings</t>
+        </is>
+      </c>
+      <c r="D267" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="18" customHeight="1">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    05-14329-06540</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="n"/>
+      <c r="C269" s="5" t="n"/>
+      <c r="D269" s="6" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="7" t="inlineStr">
+        <is>
+          <t>*J14FD</t>
+        </is>
+      </c>
+      <c r="B270" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C270" s="9" t="inlineStr">
+        <is>
+          <t>JIM DUNLOP Professional Capo Flat Strap Style For Classical Guitars</t>
+        </is>
+      </c>
+      <c r="D270" s="10" t="inlineStr">
+        <is>
+          <t>Devil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="18" customHeight="1">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    05-14333-75943</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="n"/>
+      <c r="C272" s="5" t="n"/>
+      <c r="D272" s="6" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="11" t="inlineStr">
+        <is>
+          <t>*BM12177</t>
+        </is>
+      </c>
+      <c r="B273" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C273" s="13" t="inlineStr">
+        <is>
+          <t>A New Tune A Day Clarinet Book 2/CD Book</t>
+        </is>
+      </c>
+      <c r="D273" s="14" t="inlineStr">
+        <is>
+          <t>Sent Encore Aus Post Express</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="11" t="inlineStr">
+        <is>
+          <t>*420171</t>
+        </is>
+      </c>
+      <c r="B274" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C274" s="13" t="inlineStr">
+        <is>
+          <t>Piano Adventures Lesson Book 1 2nd Edition (Softcover Book)</t>
+        </is>
+      </c>
+      <c r="D274" s="14" t="inlineStr">
+        <is>
+          <t>Sent Encore Aus Post Express</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="11" t="inlineStr">
+        <is>
+          <t>*BM12166</t>
+        </is>
+      </c>
+      <c r="B275" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C275" s="13" t="inlineStr">
+        <is>
+          <t>A New Tune A Day Flute Book 2/CD Book</t>
+        </is>
+      </c>
+      <c r="D275" s="14" t="inlineStr">
+        <is>
+          <t>Sent Encore Aus Post Express</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="7" t="inlineStr">
+        <is>
+          <t>*MPT300502</t>
+        </is>
+      </c>
+      <c r="B276" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C276" s="9" t="inlineStr">
+        <is>
+          <t>Theory Made Easy For Little Children Lvl 2 (Softcover Book)</t>
+        </is>
+      </c>
+      <c r="D276" s="10" t="inlineStr">
+        <is>
+          <t>Sent Encore Untracked</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="18" customHeight="1">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    07-14325-30415</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="n"/>
+      <c r="C278" s="5" t="n"/>
+      <c r="D278" s="6" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="7" t="inlineStr">
+        <is>
+          <t>*EJ27N</t>
+        </is>
+      </c>
+      <c r="B279" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C279" s="9" t="inlineStr">
+        <is>
+          <t>3x D'Addario EJ27N Classic Nylon Guitar Strings Daddario EJ-27N *SET OF 3 PACKS*</t>
+        </is>
+      </c>
+      <c r="D279" s="10" t="inlineStr">
+        <is>
+          <t>03/10 09:55: Product issue - provided tracking info | Status: Order found</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="18" customHeight="1">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    07-14334-80650</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="n"/>
+      <c r="C281" s="5" t="n"/>
+      <c r="D281" s="6" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="7" t="inlineStr">
+        <is>
+          <t>*BX-0114-10</t>
+        </is>
+      </c>
+      <c r="B282" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C282" s="9" t="inlineStr">
+        <is>
+          <t>Remo 14" Emperor x Coated With Dot Drum Head</t>
+        </is>
+      </c>
+      <c r="D282" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="18" customHeight="1">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    07-14335-01098</t>
+        </is>
+      </c>
+      <c r="B284" s="4" t="n"/>
+      <c r="C284" s="5" t="n"/>
+      <c r="D284" s="6" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="7" t="inlineStr">
+        <is>
+          <t>*LO1910MM-C</t>
+        </is>
+      </c>
+      <c r="B285" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C285" s="9" t="inlineStr">
+        <is>
+          <t>Lee Oskar Melody Maker ( Key of C ) 1910MM-C Diatonic Harmonica Harp with case</t>
+        </is>
+      </c>
+      <c r="D285" s="10" t="inlineStr">
+        <is>
+          <t>03/08 18:56: LO1910MM-C ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="18" customHeight="1">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    08-14333-44091</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="n"/>
+      <c r="C287" s="5" t="n"/>
+      <c r="D287" s="6" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="11" t="inlineStr">
+        <is>
+          <t>*P3-0114-C2</t>
+        </is>
+      </c>
+      <c r="B288" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C288" s="13" t="inlineStr">
+        <is>
+          <t>Remo 14" Coated Powerstroke 3 Clear Dot Drum Head</t>
+        </is>
+      </c>
+      <c r="D288" s="14" t="inlineStr">
+        <is>
+          <t>03/08 18:56: P3-0114-C2 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="7" t="inlineStr">
+        <is>
+          <t>*P3-1322-C2</t>
+        </is>
+      </c>
+      <c r="B289" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C289" s="9" t="inlineStr">
+        <is>
+          <t>Remo 22" Clear Powerstroke 3 Bass Drum Head</t>
+        </is>
+      </c>
+      <c r="D289" s="10" t="inlineStr">
+        <is>
+          <t>03/08 18:56: P3-1322-C2 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="18" customHeight="1">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    09-14333-84032</t>
+        </is>
+      </c>
+      <c r="B291" s="4" t="n"/>
+      <c r="C291" s="5" t="n"/>
+      <c r="D291" s="6" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="7" t="inlineStr">
+        <is>
+          <t>*10889PT</t>
+        </is>
+      </c>
+      <c r="B292" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C292" s="9" t="inlineStr">
+        <is>
+          <t>Aquila B-Black Eco-Friendly Tenor Ukulele String Set with Wound Low G</t>
+        </is>
+      </c>
+      <c r="D292" s="10" t="inlineStr">
+        <is>
+          <t>01/29 10:23: SHIPPING | DELIVERY CONFIRMATION - Strings delivery - Customer confirmed receipt, all good.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="18" customHeight="1">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    12-14318-98622</t>
+        </is>
+      </c>
+      <c r="B294" s="4" t="n"/>
+      <c r="C294" s="5" t="n"/>
+      <c r="D294" s="6" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="7" t="inlineStr">
+        <is>
+          <t>*50270PT</t>
+        </is>
+      </c>
+      <c r="B295" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C295" s="9" t="inlineStr">
+        <is>
+          <t>Violin Bridge -Teller Germany *** Cut &amp; Fitted 3/4</t>
+        </is>
+      </c>
+      <c r="D295" s="10" t="inlineStr">
+        <is>
+          <t>Messaged about waiting - Kyal</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="18" customHeight="1">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    12-14319-46978</t>
+        </is>
+      </c>
+      <c r="B297" s="4" t="n"/>
+      <c r="C297" s="5" t="n"/>
+      <c r="D297" s="6" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="7" t="inlineStr">
+        <is>
+          <t>*ED603</t>
+        </is>
+      </c>
+      <c r="B298" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C298" s="9" t="inlineStr">
+        <is>
+          <t>CNB 63CM Glockenspiel Bag Black Nylon Waterproof with Padded Protection ED603</t>
+        </is>
+      </c>
+      <c r="D298" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="18" customHeight="1">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    12-14328-47722</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="n"/>
+      <c r="C300" s="5" t="n"/>
+      <c r="D300" s="6" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="7" t="inlineStr">
+        <is>
+          <t>*EJ32C</t>
+        </is>
+      </c>
+      <c r="B301" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C301" s="9" t="inlineStr">
+        <is>
+          <t>D'Addario EJ32C Folk Nylon Guitar Strings, Ball End, Silver Wound-Clear Nylon Tr</t>
+        </is>
+      </c>
+      <c r="D301" s="10" t="inlineStr">
+        <is>
+          <t>Devil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="18" customHeight="1">
+      <c r="A303" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    13-14318-73202</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="n"/>
+      <c r="C303" s="5" t="n"/>
+      <c r="D303" s="6" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="11" t="inlineStr">
+        <is>
+          <t>*150UPT</t>
+        </is>
+      </c>
+      <c r="B304" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C304" s="13" t="inlineStr">
+        <is>
+          <t>Jim Dunlop 1.5MM Ultex Primetone Guitar Pick - Triangle Shape</t>
+        </is>
+      </c>
+      <c r="D304" s="14" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="7" t="inlineStr">
+        <is>
+          <t>50TRI-6</t>
+        </is>
+      </c>
+      <c r="B305" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C305" s="9" t="inlineStr">
+        <is>
+          <t>6 x Jim Dunlop Tortex Triangle .50MM Gauge Guitar Picks 431R Plectrums</t>
+        </is>
+      </c>
+      <c r="D305" s="10" t="inlineStr">
+        <is>
+          <t>Mini.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="18" customHeight="1">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    13-14330-82347</t>
+        </is>
+      </c>
+      <c r="B307" s="4" t="n"/>
+      <c r="C307" s="5" t="n"/>
+      <c r="D307" s="6" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="7" t="inlineStr">
+        <is>
+          <t>*WR-TRES-3.1-GB</t>
+        </is>
+      </c>
+      <c r="B308" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C308" s="9" t="inlineStr">
+        <is>
+          <t>RockBoard TRES 3.1 with Gig Bag</t>
+        </is>
+      </c>
+      <c r="D308" s="10" t="inlineStr">
+        <is>
+          <t>03/08 18:56: WR-TRES-3.1-GB ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="18" customHeight="1">
+      <c r="A310" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    14-14316-66785</t>
+        </is>
+      </c>
+      <c r="B310" s="4" t="n"/>
+      <c r="C310" s="5" t="n"/>
+      <c r="D310" s="6" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="7" t="inlineStr">
+        <is>
+          <t>*ED591</t>
+        </is>
+      </c>
+      <c r="B311" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C311" s="9" t="inlineStr">
+        <is>
+          <t>CPK Glockenspiel Stand Adjustable Height 57-86cm, Metal Frame, Model ED591</t>
+        </is>
+      </c>
+      <c r="D311" s="10" t="inlineStr">
+        <is>
+          <t>03/10 09:53: General inquiry - provided assistance | Status: Order found</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="18" customHeight="1">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    14-14318-85308</t>
+        </is>
+      </c>
+      <c r="B313" s="4" t="n"/>
+      <c r="C313" s="5" t="n"/>
+      <c r="D313" s="6" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="7" t="inlineStr">
+        <is>
+          <t>*EXL110BT</t>
+        </is>
+      </c>
+      <c r="B314" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C314" s="9" t="inlineStr">
+        <is>
+          <t>10x D'Addario EXL110BT Balanced Tension Strings 10-46 Daddario *SET OF 10 PACKS*</t>
+        </is>
+      </c>
+      <c r="D314" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="18" customHeight="1">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    14-14328-30619</t>
+        </is>
+      </c>
+      <c r="B316" s="4" t="n"/>
+      <c r="C316" s="5" t="n"/>
+      <c r="D316" s="6" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="7" t="inlineStr">
+        <is>
+          <t>*GP8188G</t>
+        </is>
+      </c>
+      <c r="B317" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C317" s="9" t="inlineStr">
+        <is>
+          <t>Gotoh Neck Plate 5 x 6.5cm Gold</t>
+        </is>
+      </c>
+      <c r="D317" s="10" t="inlineStr">
+        <is>
+          <t>03/08 18:56: GP8188G ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="18" customHeight="1">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    15-14326-96012</t>
+        </is>
+      </c>
+      <c r="B319" s="4" t="n"/>
+      <c r="C319" s="5" t="n"/>
+      <c r="D319" s="6" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="7" t="inlineStr">
+        <is>
+          <t>*BU60</t>
+        </is>
+      </c>
+      <c r="B320" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C320" s="9" t="inlineStr">
+        <is>
+          <t>3 x Mahalo Ukulele Felt Picks 3.2mm Flat Soft Tone  Hawaiian Pack Uke</t>
+        </is>
+      </c>
+      <c r="D320" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="18" customHeight="1">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    15-14327-55973</t>
+        </is>
+      </c>
+      <c r="B322" s="4" t="n"/>
+      <c r="C322" s="5" t="n"/>
+      <c r="D322" s="6" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="7" t="inlineStr">
+        <is>
+          <t>*10837PT</t>
+        </is>
+      </c>
+      <c r="B323" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C323" s="9" t="inlineStr">
+        <is>
+          <t>Aquila Red Series Tenor Ukulele String Set with Low G 88U</t>
+        </is>
+      </c>
+      <c r="D323" s="10" t="inlineStr">
+        <is>
+          <t>Mini.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="18" customHeight="1">
+      <c r="A325" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    17-14329-14600</t>
+        </is>
+      </c>
+      <c r="B325" s="4" t="n"/>
+      <c r="C325" s="5" t="n"/>
+      <c r="D325" s="6" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="11" t="inlineStr">
+        <is>
+          <t>*TT16HG</t>
+        </is>
+      </c>
+      <c r="B326" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C326" s="13" t="inlineStr">
+        <is>
+          <t>Evans 16" Hydraulic Glass Drum Head</t>
+        </is>
+      </c>
+      <c r="D326" s="14" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="7" t="inlineStr">
+        <is>
+          <t>*TT13HG</t>
+        </is>
+      </c>
+      <c r="B327" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C327" s="9" t="inlineStr">
+        <is>
+          <t>Evans 13" Hydraulic Glass Drum Head</t>
+        </is>
+      </c>
+      <c r="D327" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="18" customHeight="1">
+      <c r="A329" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    19-14316-44655</t>
+        </is>
+      </c>
+      <c r="B329" s="4" t="n"/>
+      <c r="C329" s="5" t="n"/>
+      <c r="D329" s="6" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="7" t="inlineStr">
+        <is>
+          <t>*TT12HBG</t>
+        </is>
+      </c>
+      <c r="B330" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C330" s="9" t="inlineStr">
+        <is>
+          <t>Evans 12" Hydraulic Black Drum Head</t>
+        </is>
+      </c>
+      <c r="D330" s="10" t="inlineStr">
+        <is>
+          <t>on PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="18" customHeight="1">
+      <c r="A332" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    20-14306-85920</t>
+        </is>
+      </c>
+      <c r="B332" s="4" t="n"/>
+      <c r="C332" s="5" t="n"/>
+      <c r="D332" s="6" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="7" t="inlineStr">
+        <is>
+          <t>*MEP-ENVJD</t>
+        </is>
+      </c>
+      <c r="B333" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C333" s="9" t="inlineStr">
+        <is>
+          <t>Mooer Envelope Dynamic Auto Wah Guitar Effects Pedal</t>
+        </is>
+      </c>
+      <c r="D333" s="10" t="inlineStr">
+        <is>
+          <t>03/10 09:51: Product question - provided assistance [URGENT] | Status: Order found</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="18" customHeight="1">
+      <c r="A335" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    20-14306-88813</t>
+        </is>
+      </c>
+      <c r="B335" s="4" t="n"/>
+      <c r="C335" s="5" t="n"/>
+      <c r="D335" s="6" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="7" t="inlineStr">
+        <is>
+          <t>*BU60</t>
+        </is>
+      </c>
+      <c r="B336" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C336" s="9" t="inlineStr">
+        <is>
+          <t>3 x Mahalo Ukulele Felt Picks 3.2mm Flat Soft Tone  Hawaiian Pack Uke</t>
+        </is>
+      </c>
+      <c r="D336" s="10" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="18" customHeight="1">
+      <c r="A338" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    20-14315-30492</t>
+        </is>
+      </c>
+      <c r="B338" s="4" t="n"/>
+      <c r="C338" s="5" t="n"/>
+      <c r="D338" s="6" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="7" t="inlineStr">
+        <is>
+          <t>*MEP-ACJD</t>
+        </is>
+      </c>
+      <c r="B339" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C339" s="9" t="inlineStr">
+        <is>
+          <t>Mooer Acoustikar Acoustic Guitar Simulator Micro Guitar Effects Pedal</t>
+        </is>
+      </c>
+      <c r="D339" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="18" customHeight="1">
+      <c r="A341" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    21-14318-30310</t>
+        </is>
+      </c>
+      <c r="B341" s="4" t="n"/>
+      <c r="C341" s="5" t="n"/>
+      <c r="D341" s="6" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="7" t="inlineStr">
+        <is>
+          <t>*DB577</t>
+        </is>
+      </c>
+      <c r="B342" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C342" s="9" t="inlineStr">
+        <is>
+          <t>DXP Bass Drum Spurs with Ratchet Style Angle Adjustment - Pair</t>
+        </is>
+      </c>
+      <c r="D342" s="10" t="inlineStr">
+        <is>
+          <t>03/08 18:55: DB577 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="18" customHeight="1">
+      <c r="A344" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    25-14299-95340</t>
+        </is>
+      </c>
+      <c r="B344" s="4" t="n"/>
+      <c r="C344" s="5" t="n"/>
+      <c r="D344" s="6" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="7" t="inlineStr">
+        <is>
+          <t>*VC104WT</t>
+        </is>
+      </c>
+      <c r="B345" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C345" s="9" t="inlineStr">
+        <is>
+          <t>Valencia 100 Series VC104WT Full Size Classical Guitar in White</t>
+        </is>
+      </c>
+      <c r="D345" s="10" t="inlineStr">
+        <is>
+          <t>03/10 09:45: General inquiry - provided assistance | Status: Order found</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="18" customHeight="1">
+      <c r="A347" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    26-14298-78579</t>
+        </is>
+      </c>
+      <c r="B347" s="4" t="n"/>
+      <c r="C347" s="5" t="n"/>
+      <c r="D347" s="6" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="7" t="inlineStr">
+        <is>
+          <t>*S1044</t>
+        </is>
+      </c>
+      <c r="B348" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C348" s="9" t="inlineStr">
+        <is>
+          <t>Stentor Student I 4/4 Size Cello Outfit</t>
+        </is>
+      </c>
+      <c r="D348" s="10" t="inlineStr">
+        <is>
+          <t>03/10 09:53: General inquiry - provided assistance | Status: Order found</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="18" customHeight="1">
+      <c r="A350" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    26-14316-60714</t>
+        </is>
+      </c>
+      <c r="B350" s="4" t="n"/>
+      <c r="C350" s="5" t="n"/>
+      <c r="D350" s="6" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="7" t="inlineStr">
+        <is>
+          <t>*EP1301</t>
+        </is>
+      </c>
+      <c r="B351" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C351" s="9" t="inlineStr">
+        <is>
+          <t>DiMarzio Switchcraft 1/4" Guitar Output Jack Socket Mono Input EP1301</t>
+        </is>
+      </c>
+      <c r="D351" s="10" t="inlineStr">
+        <is>
+          <t>on po</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="110">
+    <mergeCell ref="A303:D303"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A200:D200"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A152:D152"/>
+    <mergeCell ref="A265:D265"/>
+    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A176:D176"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A258:D258"/>
+    <mergeCell ref="A329:D329"/>
+    <mergeCell ref="A347:D347"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A257:D257"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A226:D226"/>
+    <mergeCell ref="A291:D291"/>
+    <mergeCell ref="A241:D241"/>
+    <mergeCell ref="A124:D124"/>
+    <mergeCell ref="A172:D172"/>
+    <mergeCell ref="A212:D212"/>
+    <mergeCell ref="A335:D335"/>
+    <mergeCell ref="A149:D149"/>
+    <mergeCell ref="A163:D163"/>
+    <mergeCell ref="A341:D341"/>
+    <mergeCell ref="A223:D223"/>
+    <mergeCell ref="A294:D294"/>
+    <mergeCell ref="A251:D251"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A269:D269"/>
+    <mergeCell ref="A278:D278"/>
+    <mergeCell ref="A188:D188"/>
+    <mergeCell ref="A206:D206"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A127:D127"/>
+    <mergeCell ref="A319:D319"/>
+    <mergeCell ref="A232:D232"/>
+    <mergeCell ref="A216:D216"/>
+    <mergeCell ref="A191:D191"/>
+    <mergeCell ref="A169:D169"/>
+    <mergeCell ref="A316:D316"/>
+    <mergeCell ref="A177:D177"/>
+    <mergeCell ref="A90:D90"/>
+    <mergeCell ref="A136:D136"/>
+    <mergeCell ref="A272:D272"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A313:D313"/>
+    <mergeCell ref="A194:D194"/>
+    <mergeCell ref="A307:D307"/>
+    <mergeCell ref="A322:D322"/>
+    <mergeCell ref="A203:D203"/>
+    <mergeCell ref="A181:D181"/>
+    <mergeCell ref="A184:D184"/>
+    <mergeCell ref="A244:D244"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A109:D109"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="A155:D155"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A344:D344"/>
+    <mergeCell ref="A229:D229"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A310:D310"/>
+    <mergeCell ref="A166:D166"/>
+    <mergeCell ref="A350:D350"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A300:D300"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="A287:D287"/>
+    <mergeCell ref="A281:D281"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="A133:D133"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A248:D248"/>
+    <mergeCell ref="A297:D297"/>
+    <mergeCell ref="A235:D235"/>
+    <mergeCell ref="A185:D185"/>
+    <mergeCell ref="A219:D219"/>
+    <mergeCell ref="A106:D106"/>
+    <mergeCell ref="A209:D209"/>
+    <mergeCell ref="A332:D332"/>
+    <mergeCell ref="A338:D338"/>
+    <mergeCell ref="A130:D130"/>
+    <mergeCell ref="A261:D261"/>
+    <mergeCell ref="A284:D284"/>
+    <mergeCell ref="A222:D222"/>
+    <mergeCell ref="A197:D197"/>
+    <mergeCell ref="A325:D325"/>
+    <mergeCell ref="A146:D146"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A213:D213"/>
+    <mergeCell ref="A160:D160"/>
+    <mergeCell ref="A254:D254"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -608,7 +4439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -658,33 +4489,4607 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>N465376</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>KTNMINI</t>
-        </is>
-      </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>BOSS KATANA-MINI Portable Battery Guitar Amplifier - Compact Tone with Onboard Effects</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr"/>
-      <c r="F2" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>Checking ETA with Roland | Due late Jan, Messaged about waiting - Kyal | Happy to wait, Dropship organised, awaiting tracking - Kyal</t>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>N476665</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>*50982PT</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>Violin Chinrest-Wittner Spaceage 1/2-1/4</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>N476828</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>*35088PT</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Basso Floral Leather Guitar Strap - Whiskey, 7.5cm Width, Adjustable Length 1.00-1.45m, Foam Lining, Reinforced Ends</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>N476877</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>*10857PT</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Aquila ThunderBlack 140U Bass Ukulele Set</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>N476893</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>*DA570</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Xtreme Drum Hardware Bag Extra Heavy Duty Padded Bag 100Cm x 35Cm x 35Cm</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>N476901</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>*MNCC-15L-SOPJD</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>Martinez 'Natural Series' Left Handed Spruce Top Acoustic-Electric Classical Cutaway Guitar (Open Pore)</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>N476909</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>*LP008CS</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>LP Chad Smith Signature Ridge Rider Cowbell</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>N476916</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>*EDA30B</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>Carlsbro EDA30B Electronic Drum Amplifier w/ Bluetooth</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>N476919</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>*606101AUSTRALIS</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>Armour CYB250X Cymbal Bag</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>both on po | 606101AUSTRALIS in waiting area</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>N476919</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>PR9025</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>Protection Racket 15" Fleece Drum Throne Seat Cover</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr"/>
+      <c r="F17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="16" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>N476924</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>*G30P1</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>Gotoh G30 Acoustic Machine Heads 3-a-Side Chrome with White Buttons</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>N476927</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>*S14H30</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>Evans Clear 300 Snare Side Drum Head, 14 Inch *SKIN ONLY*</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>N476934</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>114FLJ3-24</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>24 x Jim Dunlop Tortex Jazz III FLEX 1.14MM Gauge Guitar Picks 468R *NEW*</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr"/>
+      <c r="F23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>114FLJ3 and NYNW072 on PO, NYXL1156 set aside</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>N476934</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>NYNW072</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>D'Addario NYXL Nickel Wound Electric Guitar Single String, .072</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr"/>
+      <c r="F24" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" s="16" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>N476934</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>*NYXL1156</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>D'Addario NYXL1156 Nickel Wound Electric Guitar Strings, Medium Top - Extra-Heavy Bottom, 11-56</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="16" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>N476940</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>*TGB-B-BLKJD</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>Tiki Deluxe Baritone Ukulele Bag (Black)</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>N476942</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>*MP-SJ34T-TGRJD</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>Martinez 'Slim Jim' 3/4 Size Student Classical Guitar Pack with Built In Tuner (Teal Green)</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>N476958</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>*ED418</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>AMS 02 Inch Hum A Zoo Kazoo - ED418</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>N476958</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>GSC42446</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>Gibraltar Standard Drum Key on Tear-off Card Display - Pk 6</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr"/>
+      <c r="F32" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="16" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>N476966</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>*ECB84</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>D'Addario ECB84 Chromes Bass Guitar Strings, Custom Light, 40-100, Long Scale</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>N476983</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>*MA410B</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>Xtreme Microphone Short Boom Stand MA410B</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>N476990</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>*MZ-BT2-KOAJD</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>Martinez Acoustic Babe Traveller Guitar (Koa)</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>N476996</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>1001133240</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>Essential Music Theory Grs 4-6 Answer Book (Softcover Book)</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr"/>
+      <c r="F40" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="16" t="inlineStr">
+        <is>
+          <t>PW-VG-01
+and cm20red on po | Books sent Encore Aus Post Express</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>N476996</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>ALF17234</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>Essentials Of Music Theory Complete Books 1-3 (Softcover Book)</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr"/>
+      <c r="F41" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="16" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>N476996</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>CM20RED</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>Cherry Metronome with Metal Mechanism &amp; Bell in Red Plastic Casing</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr"/>
+      <c r="F42" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="16" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>N476996</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>*PW-VG-01</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>Planet Waves Varigrip Adjustable Hand Exerciser</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="16" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>N476997</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>*GDVP4</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
+        <is>
+          <t>JIM DUNLOP Mini Volume x Guitar Effects Pedal *NEW* Black GDVP4</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" s="16" t="inlineStr">
+        <is>
+          <t>GDVP4 on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>N476997</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>SN-DC65</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>Strymon DC Power Cables 36inch Straight to Right Angle - 5 Pack</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr"/>
+      <c r="F46" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="16" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>N477003</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>*CP379</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>LP CP Wood Head Sng Row 10 Inch Tambourine</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" s="16" t="inlineStr">
+        <is>
+          <t>on po | centre open mon-fri 9.30am-5pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>N477006</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>*DA789</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>1 x CPK DA789 Retractable Wire Drum Brushes Black Rubber Handle</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="16" t="inlineStr">
+        <is>
+          <t>Brushes on PO, metronome set aside</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>N477006</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>WMT230WH</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>Cherub Rechargeable Digital Metronome &amp; Tuner in White</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr"/>
+      <c r="F51" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="16" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>N477010</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>*HT-AMPERO-II</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>Hotone Ampero II Multi Effects Modelling Pedal</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F53" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>N477013</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>*CX-0114-10</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <t>Remo 14" Control Sound X Coated Drum Head</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F55" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>N477033</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="inlineStr">
+        <is>
+          <t>*DA577PR</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>Xtreme DA577PR Rock Size Drum Bag Set</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F57" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>N477036</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="inlineStr">
+        <is>
+          <t>*TDH251</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="inlineStr">
+        <is>
+          <t>Mano Percussion 9/10 Inch Mini Conga Head Set Natural Hide Pair</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F59" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="16" t="inlineStr">
+        <is>
+          <t>ON PO | Please call me upon delivery.thankyou  0490928281</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>N477038</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="inlineStr">
+        <is>
+          <t>*MMR5W</t>
+        </is>
+      </c>
+      <c r="D61" s="16" t="inlineStr">
+        <is>
+          <t>Mini Multi Instrument Rack Stand with Wheels</t>
+        </is>
+      </c>
+      <c r="E61" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F61" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>N477040</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="inlineStr">
+        <is>
+          <t>*BU60</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
+        <is>
+          <t>3 x Mahalo Ukulele Felt Picks 3.2mm Flat Soft Tone  Hawaiian Pack Uke</t>
+        </is>
+      </c>
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F63" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="16" t="inlineStr">
+        <is>
+          <t>Both on PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>N477040</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr">
+        <is>
+          <t>MJ1TBR</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>Mahalo J Series Soprano Ukulele Trans Brown MJ1TBR with Gig Bag</t>
+        </is>
+      </c>
+      <c r="E64" s="15" t="inlineStr"/>
+      <c r="F64" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="16" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>N477041</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="inlineStr">
+        <is>
+          <t>*CDSP041</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>Carlsbro CSD35M Hi-Hat Pack</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F66" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>N477042</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
+          <t>*JPJLFJ</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
+          <t>JIM DUNLOP Black Jeff Loomis Custom Flow Jumbo Guitar Pick Player's Pack.</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F68" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>N477072</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>*XRC2U</t>
+        </is>
+      </c>
+      <c r="D70" s="16" t="inlineStr">
+        <is>
+          <t>Xtreme 2U Rack Mount Road Case</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F70" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="16" t="inlineStr">
+        <is>
+          <t>on po | Leave at front door if no one home</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>N477074</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>*VC204TWR</t>
+        </is>
+      </c>
+      <c r="D72" s="16" t="inlineStr">
+        <is>
+          <t>Valencia Series 200 Classical Guitar (Transparent Wine Red)</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F72" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>N477085</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>*UE863</t>
+        </is>
+      </c>
+      <c r="D74" s="16" t="inlineStr">
+        <is>
+          <t>1st Note Kazoo UE863 Assorted Colors (Single Kazoo)</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F74" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G74" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>N477113</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>*22544PT</t>
+        </is>
+      </c>
+      <c r="D76" s="16" t="inlineStr">
+        <is>
+          <t>Conductor Baton-Ebony Handle 18in</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F76" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="16" t="inlineStr">
+        <is>
+          <t>ON PO | Dropship organised, awaiting tracking - Kyal</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>N477126</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>*XSAPB1356</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
+        <is>
+          <t>D'Addario XS Coated Acoustic Phosphor Bronze Strings - Medium Set (13-56)</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F78" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>N477127</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>*SO-10</t>
+        </is>
+      </c>
+      <c r="D80" s="16" t="inlineStr">
+        <is>
+          <t>SoundOff by Evans Drum Mute, 10 Inch</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F80" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="16" t="inlineStr">
+        <is>
+          <t>SO-8 ON PO. Others set aside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>N477127</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>SO-12</t>
+        </is>
+      </c>
+      <c r="D81" s="16" t="inlineStr">
+        <is>
+          <t>SoundOff by Evans Drum Mute, 12 Inch</t>
+        </is>
+      </c>
+      <c r="E81" s="15" t="inlineStr"/>
+      <c r="F81" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="16" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>N477127</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>SO-13</t>
+        </is>
+      </c>
+      <c r="D82" s="16" t="inlineStr">
+        <is>
+          <t>SoundOff by Evans Drum Mute, 13 Inch</t>
+        </is>
+      </c>
+      <c r="E82" s="15" t="inlineStr"/>
+      <c r="F82" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="16" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>N477127</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>*SO-8</t>
+        </is>
+      </c>
+      <c r="D83" s="16" t="inlineStr">
+        <is>
+          <t>SoundOff by Evans Drum Mute, 8 Inch</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F83" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="16" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>N477128</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>*SOMS-MS2-BLKJD</t>
+        </is>
+      </c>
+      <c r="D85" s="16" t="inlineStr">
+        <is>
+          <t>SoundArt Orchestral Music Stand (Black)</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F85" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="16" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: SOMS-MS2-BLK ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>N477132</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="inlineStr">
+        <is>
+          <t>*MSD17</t>
+        </is>
+      </c>
+      <c r="D87" s="16" t="inlineStr">
+        <is>
+          <t>Platinum Extension Music Stand Attaches To Mic Stand Three Postion Black</t>
+        </is>
+      </c>
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F87" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="16" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: MSD17 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>N477146</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="inlineStr">
+        <is>
+          <t>*LP281</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="inlineStr">
+        <is>
+          <t>LP Professional Maracas</t>
+        </is>
+      </c>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F89" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="16" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: LP281 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="inlineStr">
+        <is>
+          <t>N477157</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="inlineStr">
+        <is>
+          <t>*HC3065</t>
+        </is>
+      </c>
+      <c r="D91" s="16" t="inlineStr">
+        <is>
+          <t>Xtreme HC3065 Parlour Size Acoustic Guitar Case - Black</t>
+        </is>
+      </c>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F91" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>N477193</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="inlineStr">
+        <is>
+          <t>*MPC24FS</t>
+        </is>
+      </c>
+      <c r="D93" s="16" t="inlineStr">
+        <is>
+          <t>Mano 8 inch Tuneable Djembe - Forest Spirit Finish</t>
+        </is>
+      </c>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F93" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="16" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: MPC24FS ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>N477203</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="inlineStr">
+        <is>
+          <t>BVMRK72-08-2PCMC</t>
+        </is>
+      </c>
+      <c r="D95" s="16" t="inlineStr">
+        <is>
+          <t>Boveda Humidity Control 2 pc Size 8,  72% For Single &amp;  Double Reed Storage</t>
+        </is>
+      </c>
+      <c r="E95" s="15" t="inlineStr"/>
+      <c r="F95" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="16" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: BVMRK72-08-2P, CH331, RCB1015, WSCORK ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B96" s="15" t="inlineStr">
+        <is>
+          <t>N477203</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="inlineStr">
+        <is>
+          <t>CH331</t>
+        </is>
+      </c>
+      <c r="D96" s="16" t="inlineStr">
+        <is>
+          <t>Champion CH331 Soprano Saxophone and Clarinet Pull-Through Cleaner</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="inlineStr"/>
+      <c r="F96" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="16" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>N477203</t>
+        </is>
+      </c>
+      <c r="C97" s="15" t="inlineStr">
+        <is>
+          <t>MS105</t>
+        </is>
+      </c>
+      <c r="D97" s="16" t="inlineStr">
+        <is>
+          <t>Xtreme Music Stand Tripod Base w/bag</t>
+        </is>
+      </c>
+      <c r="E97" s="15" t="inlineStr"/>
+      <c r="F97" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="16" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>N477203</t>
+        </is>
+      </c>
+      <c r="C98" s="15" t="inlineStr">
+        <is>
+          <t>*RCB1015</t>
+        </is>
+      </c>
+      <c r="D98" s="16" t="inlineStr">
+        <is>
+          <t>Rico Royal Bb Clarinet Reeds, Strength 1.5, 10-pack</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F98" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="16" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>N477203</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="inlineStr">
+        <is>
+          <t>WSCORK</t>
+        </is>
+      </c>
+      <c r="D99" s="16" t="inlineStr">
+        <is>
+          <t>Superslick Cork Grease Lipstick Style Dispenser</t>
+        </is>
+      </c>
+      <c r="E99" s="15" t="inlineStr"/>
+      <c r="F99" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="16" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>N477215</t>
+        </is>
+      </c>
+      <c r="C101" s="15" t="inlineStr">
+        <is>
+          <t>*RMP01B</t>
+        </is>
+      </c>
+      <c r="D101" s="16" t="inlineStr">
+        <is>
+          <t>Reserve Mouthpiece Patch, Black, 5 pack</t>
+        </is>
+      </c>
+      <c r="E101" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F101" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="16" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: RMP01B ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B103" s="15" t="inlineStr">
+        <is>
+          <t>N477247</t>
+        </is>
+      </c>
+      <c r="C103" s="15" t="inlineStr">
+        <is>
+          <t>*EDP002</t>
+        </is>
+      </c>
+      <c r="D103" s="16" t="inlineStr">
+        <is>
+          <t>DXP 32-Note Chromatic Glockenspiel, F5 - C8 with Nylon Beaters and Rack</t>
+        </is>
+      </c>
+      <c r="E103" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F103" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B105" s="15" t="inlineStr">
+        <is>
+          <t>N477249</t>
+        </is>
+      </c>
+      <c r="C105" s="15" t="inlineStr">
+        <is>
+          <t>*DA581</t>
+        </is>
+      </c>
+      <c r="D105" s="16" t="inlineStr">
+        <is>
+          <t>22" Cymbal Bag</t>
+        </is>
+      </c>
+      <c r="E105" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F105" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B107" s="15" t="inlineStr">
+        <is>
+          <t>N477267</t>
+        </is>
+      </c>
+      <c r="C107" s="15" t="inlineStr">
+        <is>
+          <t>*J27H04</t>
+        </is>
+      </c>
+      <c r="D107" s="16" t="inlineStr">
+        <is>
+          <t>D'Addario J27H04  Student Nylon Classical Guitar Single String, Hard Tension, Fourth String</t>
+        </is>
+      </c>
+      <c r="E107" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F107" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B109" s="15" t="inlineStr">
+        <is>
+          <t>N477271</t>
+        </is>
+      </c>
+      <c r="C109" s="15" t="inlineStr">
+        <is>
+          <t>*108495PT</t>
+        </is>
+      </c>
+      <c r="D109" s="16" t="inlineStr">
+        <is>
+          <t>Aquila Super Nylgut Baritone Ukulele String Set - Low D Tuning 128U</t>
+        </is>
+      </c>
+      <c r="E109" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F109" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="16" t="inlineStr">
+        <is>
+          <t>ej88b
+108495 both on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>N477271</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="inlineStr">
+        <is>
+          <t>AQ129U</t>
+        </is>
+      </c>
+      <c r="D110" s="16" t="inlineStr">
+        <is>
+          <t>Aquila Super Nylgut High-G Baritone Ukulele Strings Set</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="inlineStr"/>
+      <c r="F110" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="16" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B111" s="15" t="inlineStr">
+        <is>
+          <t>N477271</t>
+        </is>
+      </c>
+      <c r="C111" s="15" t="inlineStr">
+        <is>
+          <t>*EJ88B</t>
+        </is>
+      </c>
+      <c r="D111" s="16" t="inlineStr">
+        <is>
+          <t>D'Addario EJ88B Nyltech Ukulele Strings, Baritone</t>
+        </is>
+      </c>
+      <c r="E111" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F111" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="16" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B113" s="15" t="inlineStr">
+        <is>
+          <t>N477274</t>
+        </is>
+      </c>
+      <c r="C113" s="15" t="inlineStr">
+        <is>
+          <t>*EJ26-10P</t>
+        </is>
+      </c>
+      <c r="D113" s="16" t="inlineStr">
+        <is>
+          <t>D'Addario EJ26-10P Phosphor Bronze Acoustic Guitar Strings, Custom Light, 11-52, 10 Sets</t>
+        </is>
+      </c>
+      <c r="E113" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F113" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B115" s="15" t="inlineStr">
+        <is>
+          <t>N477299</t>
+        </is>
+      </c>
+      <c r="C115" s="15" t="inlineStr">
+        <is>
+          <t>*RJA1025</t>
+        </is>
+      </c>
+      <c r="D115" s="16" t="inlineStr">
+        <is>
+          <t>Rico Alto Sax Reeds, Strength 2.5, 10-pack</t>
+        </is>
+      </c>
+      <c r="E115" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F115" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B117" s="15" t="inlineStr">
+        <is>
+          <t>N477315</t>
+        </is>
+      </c>
+      <c r="C117" s="15" t="inlineStr">
+        <is>
+          <t>*UE806</t>
+        </is>
+      </c>
+      <c r="D117" s="16" t="inlineStr">
+        <is>
+          <t>Mano Percussion 8 Note Coloured Xylo C6-C7 Solid Wood</t>
+        </is>
+      </c>
+      <c r="E117" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F117" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B119" s="15" t="inlineStr">
+        <is>
+          <t>N477329</t>
+        </is>
+      </c>
+      <c r="C119" s="15" t="inlineStr">
+        <is>
+          <t>*DD2200JPS</t>
+        </is>
+      </c>
+      <c r="D119" s="16" t="inlineStr">
+        <is>
+          <t>Dimarzio John Petrucci Cliplock Guitar Strap Adjustable 35"-51</t>
+        </is>
+      </c>
+      <c r="E119" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F119" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B121" s="15" t="inlineStr">
+        <is>
+          <t>N477336</t>
+        </is>
+      </c>
+      <c r="C121" s="15" t="inlineStr">
+        <is>
+          <t>*J5006PK</t>
+        </is>
+      </c>
+      <c r="D121" s="16" t="inlineStr">
+        <is>
+          <t>Jim Dunlop Ergo Pick Holder</t>
+        </is>
+      </c>
+      <c r="E121" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F121" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="16" t="inlineStr">
+        <is>
+          <t>both on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="15" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B122" s="15" t="inlineStr">
+        <is>
+          <t>N477336</t>
+        </is>
+      </c>
+      <c r="C122" s="15" t="inlineStr">
+        <is>
+          <t>J7007</t>
+        </is>
+      </c>
+      <c r="D122" s="16" t="inlineStr">
+        <is>
+          <t>Dunlop Ergonomic Guitar Pick Shaped Strap Lock</t>
+        </is>
+      </c>
+      <c r="E122" s="15" t="inlineStr"/>
+      <c r="F122" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="16" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="15" t="inlineStr">
+        <is>
+          <t>Amazon AU</t>
+        </is>
+      </c>
+      <c r="B124" s="15" t="inlineStr">
+        <is>
+          <t>N476962</t>
+        </is>
+      </c>
+      <c r="C124" s="15" t="inlineStr">
+        <is>
+          <t>RIA0315</t>
+        </is>
+      </c>
+      <c r="D124" s="16" t="inlineStr">
+        <is>
+          <t>Rico Soprano Sax Reeds, Strength 1.5, 3-pack</t>
+        </is>
+      </c>
+      <c r="E124" s="15" t="inlineStr"/>
+      <c r="F124" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="16" t="inlineStr">
+        <is>
+          <t>Reeds set aside, mouthpiece on PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="15" t="inlineStr">
+        <is>
+          <t>Amazon AU</t>
+        </is>
+      </c>
+      <c r="B125" s="15" t="inlineStr">
+        <is>
+          <t>N476962</t>
+        </is>
+      </c>
+      <c r="C125" s="15" t="inlineStr">
+        <is>
+          <t>*RRGMPCSSXB3</t>
+        </is>
+      </c>
+      <c r="D125" s="16" t="inlineStr">
+        <is>
+          <t>Rico Graftonite Soprano Sax Mouthpiece, B3</t>
+        </is>
+      </c>
+      <c r="E125" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F125" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="16" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="15" t="inlineStr">
+        <is>
+          <t>Amazon AU</t>
+        </is>
+      </c>
+      <c r="B127" s="15" t="inlineStr">
+        <is>
+          <t>N477290</t>
+        </is>
+      </c>
+      <c r="C127" s="15" t="inlineStr">
+        <is>
+          <t>*J3004</t>
+        </is>
+      </c>
+      <c r="D127" s="16" t="inlineStr">
+        <is>
+          <t>D'Addario J3004 Rectified Classical Guitar Single String, Normal Tension, Fourth String</t>
+        </is>
+      </c>
+      <c r="E127" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F127" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="15" t="inlineStr">
+        <is>
+          <t>BigW</t>
+        </is>
+      </c>
+      <c r="B129" s="15" t="inlineStr">
+        <is>
+          <t>N476886</t>
+        </is>
+      </c>
+      <c r="C129" s="15" t="inlineStr">
+        <is>
+          <t>*28470PT</t>
+        </is>
+      </c>
+      <c r="D129" s="16" t="inlineStr">
+        <is>
+          <t>Violin Bridge Aubert France 5 Prepared 4/4</t>
+        </is>
+      </c>
+      <c r="E129" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F129" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G129" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="15" t="inlineStr">
+        <is>
+          <t>BigW</t>
+        </is>
+      </c>
+      <c r="B131" s="15" t="inlineStr">
+        <is>
+          <t>N476929</t>
+        </is>
+      </c>
+      <c r="C131" s="15" t="inlineStr">
+        <is>
+          <t>*ROK20BL</t>
+        </is>
+      </c>
+      <c r="D131" s="16" t="inlineStr">
+        <is>
+          <t>Carson Cable Co Rocklines 20ft Braided Blue Guitar Cable with Straight Jacks</t>
+        </is>
+      </c>
+      <c r="E131" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F131" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="15" t="inlineStr">
+        <is>
+          <t>BigW</t>
+        </is>
+      </c>
+      <c r="B133" s="15" t="inlineStr">
+        <is>
+          <t>N476945</t>
+        </is>
+      </c>
+      <c r="C133" s="15" t="inlineStr">
+        <is>
+          <t>*D137A</t>
+        </is>
+      </c>
+      <c r="D133" s="16" t="inlineStr">
+        <is>
+          <t>DXP 7A OAK Wood Tip Drum Sticks</t>
+        </is>
+      </c>
+      <c r="E133" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F133" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="15" t="inlineStr">
+        <is>
+          <t>BigW</t>
+        </is>
+      </c>
+      <c r="B135" s="15" t="inlineStr">
+        <is>
+          <t>N476975</t>
+        </is>
+      </c>
+      <c r="C135" s="15" t="inlineStr">
+        <is>
+          <t>*ROK20SS</t>
+        </is>
+      </c>
+      <c r="D135" s="16" t="inlineStr">
+        <is>
+          <t>Carson Cable Co Rocklines 20ft Noiseless Guitar Cable with Straight Jacks</t>
+        </is>
+      </c>
+      <c r="E135" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F135" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G135" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="15" t="inlineStr">
+        <is>
+          <t>BigW</t>
+        </is>
+      </c>
+      <c r="B137" s="15" t="inlineStr">
+        <is>
+          <t>N477166</t>
+        </is>
+      </c>
+      <c r="C137" s="15" t="inlineStr">
+        <is>
+          <t>*JPP315</t>
+        </is>
+      </c>
+      <c r="D137" s="16" t="inlineStr">
+        <is>
+          <t>Dunlop 1.5mm Primetone Standard Guitar Picks with Grip Players Pack</t>
+        </is>
+      </c>
+      <c r="E137" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F137" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="16" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: JPP315 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="15" t="inlineStr">
+        <is>
+          <t>BigW</t>
+        </is>
+      </c>
+      <c r="B139" s="15" t="inlineStr">
+        <is>
+          <t>N477222</t>
+        </is>
+      </c>
+      <c r="C139" s="15" t="inlineStr">
+        <is>
+          <t>*HC298</t>
+        </is>
+      </c>
+      <c r="D139" s="16" t="inlineStr">
+        <is>
+          <t>CNB V-CASE Shaped Banjo Case with Black Vinyl and Orange Stitching</t>
+        </is>
+      </c>
+      <c r="E139" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F139" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="16" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:43: HC298 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="15" t="inlineStr">
+        <is>
+          <t>BigW</t>
+        </is>
+      </c>
+      <c r="B141" s="15" t="inlineStr">
+        <is>
+          <t>N477258</t>
+        </is>
+      </c>
+      <c r="C141" s="15" t="inlineStr">
+        <is>
+          <t>*MA409</t>
+        </is>
+      </c>
+      <c r="D141" s="16" t="inlineStr">
+        <is>
+          <t>AMS MA409 Heavy Duty Mic Boom Stand with 80cm Boom Arm, Chrome Finish</t>
+        </is>
+      </c>
+      <c r="E141" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F141" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="15" t="inlineStr">
+        <is>
+          <t>BigW</t>
+        </is>
+      </c>
+      <c r="B143" s="15" t="inlineStr">
+        <is>
+          <t>N477291</t>
+        </is>
+      </c>
+      <c r="C143" s="15" t="inlineStr">
+        <is>
+          <t>*CHST-65JD</t>
+        </is>
+      </c>
+      <c r="D143" s="16" t="inlineStr">
+        <is>
+          <t>Crossfire Clip-On Headstock Tuner for Guitar  Bass  Ukulele &amp; Violin</t>
+        </is>
+      </c>
+      <c r="E143" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F143" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="15" t="inlineStr">
+        <is>
+          <t>BigW</t>
+        </is>
+      </c>
+      <c r="B145" s="15" t="inlineStr">
+        <is>
+          <t>N477330</t>
+        </is>
+      </c>
+      <c r="C145" s="15" t="inlineStr">
+        <is>
+          <t>*UE848R</t>
+        </is>
+      </c>
+      <c r="D145" s="16" t="inlineStr">
+        <is>
+          <t>Mano 8 Inch Hand Drum Red with Wooden Shell and Mallet Included</t>
+        </is>
+      </c>
+      <c r="E145" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F145" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="15" t="inlineStr">
+        <is>
+          <t>EverydayMarket</t>
+        </is>
+      </c>
+      <c r="B147" s="15" t="inlineStr">
+        <is>
+          <t>N476819</t>
+        </is>
+      </c>
+      <c r="C147" s="15" t="inlineStr">
+        <is>
+          <t>*UE862</t>
+        </is>
+      </c>
+      <c r="D147" s="16" t="inlineStr">
+        <is>
+          <t>Mano Percussion MP Percussion Pack - 8-Piece Set with Carry Bag</t>
+        </is>
+      </c>
+      <c r="E147" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F147" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="15" t="inlineStr">
+        <is>
+          <t>EverydayMarket</t>
+        </is>
+      </c>
+      <c r="B149" s="15" t="inlineStr">
+        <is>
+          <t>N477195</t>
+        </is>
+      </c>
+      <c r="C149" s="15" t="inlineStr">
+        <is>
+          <t>*KOR3</t>
+        </is>
+      </c>
+      <c r="D149" s="16" t="inlineStr">
+        <is>
+          <t>Kwikfret Orange Oil 100ml Fretboard Cleaner and Protector</t>
+        </is>
+      </c>
+      <c r="E149" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F149" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" s="16" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: KOR3 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="15" t="inlineStr">
+        <is>
+          <t>EverydayMarket</t>
+        </is>
+      </c>
+      <c r="B151" s="15" t="inlineStr">
+        <is>
+          <t>N477218</t>
+        </is>
+      </c>
+      <c r="C151" s="15" t="inlineStr">
+        <is>
+          <t>*KOR3</t>
+        </is>
+      </c>
+      <c r="D151" s="16" t="inlineStr">
+        <is>
+          <t>Kwikfret Orange Oil 100ml Fretboard Cleaner and Protector</t>
+        </is>
+      </c>
+      <c r="E151" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F151" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G151" s="16" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: KOR3 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="15" t="inlineStr">
+        <is>
+          <t>Kogan</t>
+        </is>
+      </c>
+      <c r="B153" s="15" t="inlineStr">
+        <is>
+          <t>N476826</t>
+        </is>
+      </c>
+      <c r="C153" s="15" t="inlineStr">
+        <is>
+          <t>*71816PT</t>
+        </is>
+      </c>
+      <c r="D153" s="16" t="inlineStr">
+        <is>
+          <t>Pickboy Nylon Pro Guitar Picks - 12 Pack, 0.70mm, Made in Japan</t>
+        </is>
+      </c>
+      <c r="E153" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F153" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="15" t="inlineStr">
+        <is>
+          <t>Kogan</t>
+        </is>
+      </c>
+      <c r="B155" s="15" t="inlineStr">
+        <is>
+          <t>N476913</t>
+        </is>
+      </c>
+      <c r="C155" s="15" t="inlineStr">
+        <is>
+          <t>*1408107638</t>
+        </is>
+      </c>
+      <c r="D155" s="16" t="inlineStr">
+        <is>
+          <t>Abracadabra Saxophone Book Only 3rd Ed (Softcover Book)</t>
+        </is>
+      </c>
+      <c r="E155" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F155" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="16" t="inlineStr">
+        <is>
+          <t>Dropship organised, awaiting tracking - Kyal</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="15" t="inlineStr">
+        <is>
+          <t>Kogan</t>
+        </is>
+      </c>
+      <c r="B157" s="15" t="inlineStr">
+        <is>
+          <t>N477025</t>
+        </is>
+      </c>
+      <c r="C157" s="15" t="inlineStr">
+        <is>
+          <t>*VC103BUS</t>
+        </is>
+      </c>
+      <c r="D157" s="16" t="inlineStr">
+        <is>
+          <t>Valencia 3/4 Size Nylon String Student Guitar Blue</t>
+        </is>
+      </c>
+      <c r="E157" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F157" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="15" t="inlineStr">
+        <is>
+          <t>Kogan</t>
+        </is>
+      </c>
+      <c r="B159" s="15" t="inlineStr">
+        <is>
+          <t>N477050</t>
+        </is>
+      </c>
+      <c r="C159" s="15" t="inlineStr">
+        <is>
+          <t>*DSC316</t>
+        </is>
+      </c>
+      <c r="D159" s="16" t="inlineStr">
+        <is>
+          <t>DXP 16 Inch Crash Cymbal - Alloy</t>
+        </is>
+      </c>
+      <c r="E159" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F159" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="15" t="inlineStr">
+        <is>
+          <t>Kogan</t>
+        </is>
+      </c>
+      <c r="B161" s="15" t="inlineStr">
+        <is>
+          <t>N477051</t>
+        </is>
+      </c>
+      <c r="C161" s="15" t="inlineStr">
+        <is>
+          <t>1CAB4-15BT2</t>
+        </is>
+      </c>
+      <c r="D161" s="16" t="inlineStr">
+        <is>
+          <t>Planet Waves Beatles Signature Guitar Pick Tins, Stripes</t>
+        </is>
+      </c>
+      <c r="E161" s="15" t="inlineStr"/>
+      <c r="F161" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G161" s="16" t="inlineStr">
+        <is>
+          <t>all on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="15" t="inlineStr">
+        <is>
+          <t>Kogan</t>
+        </is>
+      </c>
+      <c r="B162" s="15" t="inlineStr">
+        <is>
+          <t>N477051</t>
+        </is>
+      </c>
+      <c r="C162" s="15" t="inlineStr">
+        <is>
+          <t>*RN10</t>
+        </is>
+      </c>
+      <c r="D162" s="16" t="inlineStr">
+        <is>
+          <t>Danelectro Honeytone Mini Amp Burgundy Battery Powered</t>
+        </is>
+      </c>
+      <c r="E162" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F162" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" s="16" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="15" t="inlineStr">
+        <is>
+          <t>Kogan</t>
+        </is>
+      </c>
+      <c r="B163" s="15" t="inlineStr">
+        <is>
+          <t>N477051</t>
+        </is>
+      </c>
+      <c r="C163" s="15" t="inlineStr">
+        <is>
+          <t>*RN10A</t>
+        </is>
+      </c>
+      <c r="D163" s="16" t="inlineStr">
+        <is>
+          <t>Danelectro Honeytone Mini Amplifier Aqua</t>
+        </is>
+      </c>
+      <c r="E163" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F163" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" s="16" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="15" t="inlineStr">
+        <is>
+          <t>Kogan</t>
+        </is>
+      </c>
+      <c r="B164" s="15" t="inlineStr">
+        <is>
+          <t>N477051</t>
+        </is>
+      </c>
+      <c r="C164" s="15" t="inlineStr">
+        <is>
+          <t>*RN10B</t>
+        </is>
+      </c>
+      <c r="D164" s="16" t="inlineStr">
+        <is>
+          <t>Danelectro Honeytone Mini Amp Battery Powered - RN10 Series</t>
+        </is>
+      </c>
+      <c r="E164" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F164" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" s="16" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="15" t="inlineStr">
+        <is>
+          <t>Kogan</t>
+        </is>
+      </c>
+      <c r="B166" s="15" t="inlineStr">
+        <is>
+          <t>N477053</t>
+        </is>
+      </c>
+      <c r="C166" s="15" t="inlineStr">
+        <is>
+          <t>*UE776</t>
+        </is>
+      </c>
+      <c r="D166" s="16" t="inlineStr">
+        <is>
+          <t>Mano Percussion 10 Inch Tunable Tambour with 8 Lugs</t>
+        </is>
+      </c>
+      <c r="E166" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F166" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="15" t="inlineStr">
+        <is>
+          <t>Kogan</t>
+        </is>
+      </c>
+      <c r="B168" s="15" t="inlineStr">
+        <is>
+          <t>N477060</t>
+        </is>
+      </c>
+      <c r="C168" s="15" t="inlineStr">
+        <is>
+          <t>*MINI-PSU</t>
+        </is>
+      </c>
+      <c r="D168" s="16" t="inlineStr">
+        <is>
+          <t>Laney Power Supply for Mini Amps - 12V DC 2A</t>
+        </is>
+      </c>
+      <c r="E168" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F168" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G168" s="16" t="inlineStr">
+        <is>
+          <t>both on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="15" t="inlineStr">
+        <is>
+          <t>Kogan</t>
+        </is>
+      </c>
+      <c r="B169" s="15" t="inlineStr">
+        <is>
+          <t>N477060</t>
+        </is>
+      </c>
+      <c r="C169" s="15" t="inlineStr">
+        <is>
+          <t>*MINISTACK-B-LION</t>
+        </is>
+      </c>
+      <c r="D169" s="16" t="inlineStr">
+        <is>
+          <t>Laney Lionheart Ministack Bluetooth Guitar Amplifier</t>
+        </is>
+      </c>
+      <c r="E169" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F169" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" s="16" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="15" t="inlineStr">
+        <is>
+          <t>Kogan</t>
+        </is>
+      </c>
+      <c r="B171" s="15" t="inlineStr">
+        <is>
+          <t>N477134</t>
+        </is>
+      </c>
+      <c r="C171" s="15" t="inlineStr">
+        <is>
+          <t>*CDSP035</t>
+        </is>
+      </c>
+      <c r="D171" s="16" t="inlineStr">
+        <is>
+          <t>Carlsbro CSD25M Cable Loom for CSD25M, CSD35M1, CSD45M Models</t>
+        </is>
+      </c>
+      <c r="E171" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F171" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" s="16" t="inlineStr">
+        <is>
+          <t>08/03/2026 18:56: CDSP035 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="15" t="inlineStr">
+        <is>
+          <t>Kogan</t>
+        </is>
+      </c>
+      <c r="B173" s="15" t="inlineStr">
+        <is>
+          <t>N477173</t>
+        </is>
+      </c>
+      <c r="C173" s="15" t="inlineStr">
+        <is>
+          <t>*1408107638</t>
+        </is>
+      </c>
+      <c r="D173" s="16" t="inlineStr">
+        <is>
+          <t>Abracadabra Saxophone Book Only 3rd Ed (Softcover Book)</t>
+        </is>
+      </c>
+      <c r="E173" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F173" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G173" s="16" t="inlineStr">
+        <is>
+          <t>Dropship organised, awaiting tracking - Kyal</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="15" t="inlineStr">
+        <is>
+          <t>Kogan</t>
+        </is>
+      </c>
+      <c r="B175" s="15" t="inlineStr">
+        <is>
+          <t>N477236</t>
+        </is>
+      </c>
+      <c r="C175" s="15" t="inlineStr">
+        <is>
+          <t>*MA367</t>
+        </is>
+      </c>
+      <c r="D175" s="16" t="inlineStr">
+        <is>
+          <t>AMS Mic Stand Chrome</t>
+        </is>
+      </c>
+      <c r="E175" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F175" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" s="16" t="inlineStr">
+        <is>
+          <t>09/03/2026 10:43: MA367 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B177" s="15" t="inlineStr">
+        <is>
+          <t>01-14338-85679</t>
+        </is>
+      </c>
+      <c r="C177" s="15" t="inlineStr">
+        <is>
+          <t>*MEP-12V2AJD</t>
+        </is>
+      </c>
+      <c r="D177" s="16" t="inlineStr">
+        <is>
+          <t>Mooer 12 Volt DC 2 Amp Effects Pedal Power Supply</t>
+        </is>
+      </c>
+      <c r="E177" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F177" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B179" s="15" t="inlineStr">
+        <is>
+          <t>03-14227-69047</t>
+        </is>
+      </c>
+      <c r="C179" s="15" t="inlineStr">
+        <is>
+          <t>*EDA30B</t>
+        </is>
+      </c>
+      <c r="D179" s="16" t="inlineStr">
+        <is>
+          <t>Carlsbro EDA30B Electronic Drum Amplifier w/ Bluetooth</t>
+        </is>
+      </c>
+      <c r="E179" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F179" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" s="16" t="inlineStr">
+        <is>
+          <t>in collect area, customer contacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B180" s="15" t="inlineStr">
+        <is>
+          <t>03-14227-69047</t>
+        </is>
+      </c>
+      <c r="C180" s="15" t="inlineStr">
+        <is>
+          <t>71MG50GFXEF</t>
+        </is>
+      </c>
+      <c r="D180" s="16" t="inlineStr">
+        <is>
+          <t>Marshall MG50GFX: 50W MG Gold Combo</t>
+        </is>
+      </c>
+      <c r="E180" s="15" t="inlineStr"/>
+      <c r="F180" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" s="16" t="inlineStr">
+        <is>
+          <t>in collect area, customer contacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B182" s="15" t="inlineStr">
+        <is>
+          <t>04-14343-35529</t>
+        </is>
+      </c>
+      <c r="C182" s="15" t="inlineStr">
+        <is>
+          <t>*JPTJH3</t>
+        </is>
+      </c>
+      <c r="D182" s="16" t="inlineStr">
+        <is>
+          <t>Jim Dunlop Tortex Jazz H3 Player Pack Guitar Picks 1.14 mm</t>
+        </is>
+      </c>
+      <c r="E182" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F182" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G182" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B183" s="15" t="inlineStr">
+        <is>
+          <t>04-14343-35529</t>
+        </is>
+      </c>
+      <c r="C183" s="15" t="inlineStr">
+        <is>
+          <t>PL015-10</t>
+        </is>
+      </c>
+      <c r="D183" s="16" t="inlineStr">
+        <is>
+          <t>10 x D'Addario PL015 Single Plain Steel .015 Acoustic or Electric Guitar Strings</t>
+        </is>
+      </c>
+      <c r="E183" s="15" t="inlineStr"/>
+      <c r="F183" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B185" s="15" t="inlineStr">
+        <is>
+          <t>05-14329-06540</t>
+        </is>
+      </c>
+      <c r="C185" s="15" t="inlineStr">
+        <is>
+          <t>*J14FD</t>
+        </is>
+      </c>
+      <c r="D185" s="16" t="inlineStr">
+        <is>
+          <t>JIM DUNLOP Professional Capo Flat Strap Style For Classical Guitars</t>
+        </is>
+      </c>
+      <c r="E185" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F185" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" s="16" t="inlineStr">
+        <is>
+          <t>Devil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B187" s="15" t="inlineStr">
+        <is>
+          <t>05-14333-75943</t>
+        </is>
+      </c>
+      <c r="C187" s="15" t="inlineStr">
+        <is>
+          <t>*BM12177</t>
+        </is>
+      </c>
+      <c r="D187" s="16" t="inlineStr">
+        <is>
+          <t>A New Tune A Day Clarinet Book 2/CD Book</t>
+        </is>
+      </c>
+      <c r="E187" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F187" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G187" s="16" t="inlineStr">
+        <is>
+          <t>Sent Encore Aus Post Express</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B188" s="15" t="inlineStr">
+        <is>
+          <t>05-14333-75943</t>
+        </is>
+      </c>
+      <c r="C188" s="15" t="inlineStr">
+        <is>
+          <t>*420171</t>
+        </is>
+      </c>
+      <c r="D188" s="16" t="inlineStr">
+        <is>
+          <t>Piano Adventures Lesson Book 1 2nd Edition (Softcover Book)</t>
+        </is>
+      </c>
+      <c r="E188" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F188" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" s="16" t="inlineStr">
+        <is>
+          <t>Sent Encore Aus Post Express</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B189" s="15" t="inlineStr">
+        <is>
+          <t>05-14333-75943</t>
+        </is>
+      </c>
+      <c r="C189" s="15" t="inlineStr">
+        <is>
+          <t>*BM12166</t>
+        </is>
+      </c>
+      <c r="D189" s="16" t="inlineStr">
+        <is>
+          <t>A New Tune A Day Flute Book 2/CD Book</t>
+        </is>
+      </c>
+      <c r="E189" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F189" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" s="16" t="inlineStr">
+        <is>
+          <t>Sent Encore Aus Post Express</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B190" s="15" t="inlineStr">
+        <is>
+          <t>05-14333-75943</t>
+        </is>
+      </c>
+      <c r="C190" s="15" t="inlineStr">
+        <is>
+          <t>*MPT300502</t>
+        </is>
+      </c>
+      <c r="D190" s="16" t="inlineStr">
+        <is>
+          <t>Theory Made Easy For Little Children Lvl 2 (Softcover Book)</t>
+        </is>
+      </c>
+      <c r="E190" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F190" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" s="16" t="inlineStr">
+        <is>
+          <t>Sent Encore Untracked</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B192" s="15" t="inlineStr">
+        <is>
+          <t>07-14325-30415</t>
+        </is>
+      </c>
+      <c r="C192" s="15" t="inlineStr">
+        <is>
+          <t>*EJ27N</t>
+        </is>
+      </c>
+      <c r="D192" s="16" t="inlineStr">
+        <is>
+          <t>3x D'Addario EJ27N Classic Nylon Guitar Strings Daddario EJ-27N *SET OF 3 PACKS*</t>
+        </is>
+      </c>
+      <c r="E192" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F192" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" s="16" t="inlineStr">
+        <is>
+          <t>03/10 09:55: Product issue - provided tracking info | Status: Order found</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B194" s="15" t="inlineStr">
+        <is>
+          <t>07-14334-80650</t>
+        </is>
+      </c>
+      <c r="C194" s="15" t="inlineStr">
+        <is>
+          <t>*BX-0114-10</t>
+        </is>
+      </c>
+      <c r="D194" s="16" t="inlineStr">
+        <is>
+          <t>Remo 14" Emperor x Coated With Dot Drum Head</t>
+        </is>
+      </c>
+      <c r="E194" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F194" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B196" s="15" t="inlineStr">
+        <is>
+          <t>07-14335-01098</t>
+        </is>
+      </c>
+      <c r="C196" s="15" t="inlineStr">
+        <is>
+          <t>*LO1910MM-C</t>
+        </is>
+      </c>
+      <c r="D196" s="16" t="inlineStr">
+        <is>
+          <t>Lee Oskar Melody Maker ( Key of C ) 1910MM-C Diatonic Harmonica Harp with case</t>
+        </is>
+      </c>
+      <c r="E196" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F196" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" s="16" t="inlineStr">
+        <is>
+          <t>03/08 18:56: LO1910MM-C ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B198" s="15" t="inlineStr">
+        <is>
+          <t>08-14333-44091</t>
+        </is>
+      </c>
+      <c r="C198" s="15" t="inlineStr">
+        <is>
+          <t>*P3-0114-C2</t>
+        </is>
+      </c>
+      <c r="D198" s="16" t="inlineStr">
+        <is>
+          <t>Remo 14" Coated Powerstroke 3 Clear Dot Drum Head</t>
+        </is>
+      </c>
+      <c r="E198" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F198" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" s="16" t="inlineStr">
+        <is>
+          <t>03/08 18:56: P3-0114-C2 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B199" s="15" t="inlineStr">
+        <is>
+          <t>08-14333-44091</t>
+        </is>
+      </c>
+      <c r="C199" s="15" t="inlineStr">
+        <is>
+          <t>*P3-1322-C2</t>
+        </is>
+      </c>
+      <c r="D199" s="16" t="inlineStr">
+        <is>
+          <t>Remo 22" Clear Powerstroke 3 Bass Drum Head</t>
+        </is>
+      </c>
+      <c r="E199" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F199" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" s="16" t="inlineStr">
+        <is>
+          <t>03/08 18:56: P3-1322-C2 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B201" s="15" t="inlineStr">
+        <is>
+          <t>09-14333-84032</t>
+        </is>
+      </c>
+      <c r="C201" s="15" t="inlineStr">
+        <is>
+          <t>*10889PT</t>
+        </is>
+      </c>
+      <c r="D201" s="16" t="inlineStr">
+        <is>
+          <t>Aquila B-Black Eco-Friendly Tenor Ukulele String Set with Wound Low G</t>
+        </is>
+      </c>
+      <c r="E201" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F201" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" s="16" t="inlineStr">
+        <is>
+          <t>01/29 10:23: SHIPPING | DELIVERY CONFIRMATION - Strings delivery - Customer confirmed receipt, all good.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B203" s="15" t="inlineStr">
+        <is>
+          <t>12-14318-98622</t>
+        </is>
+      </c>
+      <c r="C203" s="15" t="inlineStr">
+        <is>
+          <t>*50270PT</t>
+        </is>
+      </c>
+      <c r="D203" s="16" t="inlineStr">
+        <is>
+          <t>Violin Bridge -Teller Germany *** Cut &amp; Fitted 3/4</t>
+        </is>
+      </c>
+      <c r="E203" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F203" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" s="16" t="inlineStr">
+        <is>
+          <t>Messaged about waiting - Kyal</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B205" s="15" t="inlineStr">
+        <is>
+          <t>12-14319-46978</t>
+        </is>
+      </c>
+      <c r="C205" s="15" t="inlineStr">
+        <is>
+          <t>*ED603</t>
+        </is>
+      </c>
+      <c r="D205" s="16" t="inlineStr">
+        <is>
+          <t>CNB 63CM Glockenspiel Bag Black Nylon Waterproof with Padded Protection ED603</t>
+        </is>
+      </c>
+      <c r="E205" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F205" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B207" s="15" t="inlineStr">
+        <is>
+          <t>12-14328-47722</t>
+        </is>
+      </c>
+      <c r="C207" s="15" t="inlineStr">
+        <is>
+          <t>*EJ32C</t>
+        </is>
+      </c>
+      <c r="D207" s="16" t="inlineStr">
+        <is>
+          <t>D'Addario EJ32C Folk Nylon Guitar Strings, Ball End, Silver Wound-Clear Nylon Tr</t>
+        </is>
+      </c>
+      <c r="E207" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F207" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" s="16" t="inlineStr">
+        <is>
+          <t>Devil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B209" s="15" t="inlineStr">
+        <is>
+          <t>13-14318-73202</t>
+        </is>
+      </c>
+      <c r="C209" s="15" t="inlineStr">
+        <is>
+          <t>*150UPT</t>
+        </is>
+      </c>
+      <c r="D209" s="16" t="inlineStr">
+        <is>
+          <t>Jim Dunlop 1.5MM Ultex Primetone Guitar Pick - Triangle Shape</t>
+        </is>
+      </c>
+      <c r="E209" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F209" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G209" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B210" s="15" t="inlineStr">
+        <is>
+          <t>13-14318-73202</t>
+        </is>
+      </c>
+      <c r="C210" s="15" t="inlineStr">
+        <is>
+          <t>50TRI-6</t>
+        </is>
+      </c>
+      <c r="D210" s="16" t="inlineStr">
+        <is>
+          <t>6 x Jim Dunlop Tortex Triangle .50MM Gauge Guitar Picks 431R Plectrums</t>
+        </is>
+      </c>
+      <c r="E210" s="15" t="inlineStr"/>
+      <c r="F210" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G210" s="16" t="inlineStr">
+        <is>
+          <t>Mini.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B212" s="15" t="inlineStr">
+        <is>
+          <t>13-14330-82347</t>
+        </is>
+      </c>
+      <c r="C212" s="15" t="inlineStr">
+        <is>
+          <t>*WR-TRES-3.1-GB</t>
+        </is>
+      </c>
+      <c r="D212" s="16" t="inlineStr">
+        <is>
+          <t>RockBoard TRES 3.1 with Gig Bag</t>
+        </is>
+      </c>
+      <c r="E212" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F212" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" s="16" t="inlineStr">
+        <is>
+          <t>03/08 18:56: WR-TRES-3.1-GB ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B214" s="15" t="inlineStr">
+        <is>
+          <t>14-14316-66785</t>
+        </is>
+      </c>
+      <c r="C214" s="15" t="inlineStr">
+        <is>
+          <t>*ED591</t>
+        </is>
+      </c>
+      <c r="D214" s="16" t="inlineStr">
+        <is>
+          <t>CPK Glockenspiel Stand Adjustable Height 57-86cm, Metal Frame, Model ED591</t>
+        </is>
+      </c>
+      <c r="E214" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F214" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" s="16" t="inlineStr">
+        <is>
+          <t>03/10 09:53: General inquiry - provided assistance | Status: Order found</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B216" s="15" t="inlineStr">
+        <is>
+          <t>14-14318-85308</t>
+        </is>
+      </c>
+      <c r="C216" s="15" t="inlineStr">
+        <is>
+          <t>*EXL110BT</t>
+        </is>
+      </c>
+      <c r="D216" s="16" t="inlineStr">
+        <is>
+          <t>10x D'Addario EXL110BT Balanced Tension Strings 10-46 Daddario *SET OF 10 PACKS*</t>
+        </is>
+      </c>
+      <c r="E216" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F216" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G216" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B218" s="15" t="inlineStr">
+        <is>
+          <t>14-14328-30619</t>
+        </is>
+      </c>
+      <c r="C218" s="15" t="inlineStr">
+        <is>
+          <t>*GP8188G</t>
+        </is>
+      </c>
+      <c r="D218" s="16" t="inlineStr">
+        <is>
+          <t>Gotoh Neck Plate 5 x 6.5cm Gold</t>
+        </is>
+      </c>
+      <c r="E218" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F218" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G218" s="16" t="inlineStr">
+        <is>
+          <t>03/08 18:56: GP8188G ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B220" s="15" t="inlineStr">
+        <is>
+          <t>15-14326-96012</t>
+        </is>
+      </c>
+      <c r="C220" s="15" t="inlineStr">
+        <is>
+          <t>*BU60</t>
+        </is>
+      </c>
+      <c r="D220" s="16" t="inlineStr">
+        <is>
+          <t>3 x Mahalo Ukulele Felt Picks 3.2mm Flat Soft Tone  Hawaiian Pack Uke</t>
+        </is>
+      </c>
+      <c r="E220" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F220" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G220" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B222" s="15" t="inlineStr">
+        <is>
+          <t>15-14327-55973</t>
+        </is>
+      </c>
+      <c r="C222" s="15" t="inlineStr">
+        <is>
+          <t>*10837PT</t>
+        </is>
+      </c>
+      <c r="D222" s="16" t="inlineStr">
+        <is>
+          <t>Aquila Red Series Tenor Ukulele String Set with Low G 88U</t>
+        </is>
+      </c>
+      <c r="E222" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F222" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G222" s="16" t="inlineStr">
+        <is>
+          <t>Mini.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B224" s="15" t="inlineStr">
+        <is>
+          <t>17-14329-14600</t>
+        </is>
+      </c>
+      <c r="C224" s="15" t="inlineStr">
+        <is>
+          <t>*TT16HG</t>
+        </is>
+      </c>
+      <c r="D224" s="16" t="inlineStr">
+        <is>
+          <t>Evans 16" Hydraulic Glass Drum Head</t>
+        </is>
+      </c>
+      <c r="E224" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F224" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G224" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B225" s="15" t="inlineStr">
+        <is>
+          <t>17-14329-14600</t>
+        </is>
+      </c>
+      <c r="C225" s="15" t="inlineStr">
+        <is>
+          <t>*TT13HG</t>
+        </is>
+      </c>
+      <c r="D225" s="16" t="inlineStr">
+        <is>
+          <t>Evans 13" Hydraulic Glass Drum Head</t>
+        </is>
+      </c>
+      <c r="E225" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F225" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B227" s="15" t="inlineStr">
+        <is>
+          <t>19-14316-44655</t>
+        </is>
+      </c>
+      <c r="C227" s="15" t="inlineStr">
+        <is>
+          <t>*TT12HBG</t>
+        </is>
+      </c>
+      <c r="D227" s="16" t="inlineStr">
+        <is>
+          <t>Evans 12" Hydraulic Black Drum Head</t>
+        </is>
+      </c>
+      <c r="E227" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F227" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G227" s="16" t="inlineStr">
+        <is>
+          <t>on PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B229" s="15" t="inlineStr">
+        <is>
+          <t>20-14306-85920</t>
+        </is>
+      </c>
+      <c r="C229" s="15" t="inlineStr">
+        <is>
+          <t>*MEP-ENVJD</t>
+        </is>
+      </c>
+      <c r="D229" s="16" t="inlineStr">
+        <is>
+          <t>Mooer Envelope Dynamic Auto Wah Guitar Effects Pedal</t>
+        </is>
+      </c>
+      <c r="E229" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F229" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G229" s="16" t="inlineStr">
+        <is>
+          <t>03/10 09:51: Product question - provided assistance [URGENT] | Status: Order found</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B231" s="15" t="inlineStr">
+        <is>
+          <t>20-14306-88813</t>
+        </is>
+      </c>
+      <c r="C231" s="15" t="inlineStr">
+        <is>
+          <t>*BU60</t>
+        </is>
+      </c>
+      <c r="D231" s="16" t="inlineStr">
+        <is>
+          <t>3 x Mahalo Ukulele Felt Picks 3.2mm Flat Soft Tone  Hawaiian Pack Uke</t>
+        </is>
+      </c>
+      <c r="E231" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F231" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G231" s="16" t="inlineStr">
+        <is>
+          <t>ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B233" s="15" t="inlineStr">
+        <is>
+          <t>20-14315-30492</t>
+        </is>
+      </c>
+      <c r="C233" s="15" t="inlineStr">
+        <is>
+          <t>*MEP-ACJD</t>
+        </is>
+      </c>
+      <c r="D233" s="16" t="inlineStr">
+        <is>
+          <t>Mooer Acoustikar Acoustic Guitar Simulator Micro Guitar Effects Pedal</t>
+        </is>
+      </c>
+      <c r="E233" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F233" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G233" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B235" s="15" t="inlineStr">
+        <is>
+          <t>21-14318-30310</t>
+        </is>
+      </c>
+      <c r="C235" s="15" t="inlineStr">
+        <is>
+          <t>*DB577</t>
+        </is>
+      </c>
+      <c r="D235" s="16" t="inlineStr">
+        <is>
+          <t>DXP Bass Drum Spurs with Ratchet Style Angle Adjustment - Pair</t>
+        </is>
+      </c>
+      <c r="E235" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F235" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G235" s="16" t="inlineStr">
+        <is>
+          <t>03/08 18:55: DB577 ON PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B237" s="15" t="inlineStr">
+        <is>
+          <t>25-14299-95340</t>
+        </is>
+      </c>
+      <c r="C237" s="15" t="inlineStr">
+        <is>
+          <t>*VC104WT</t>
+        </is>
+      </c>
+      <c r="D237" s="16" t="inlineStr">
+        <is>
+          <t>Valencia 100 Series VC104WT Full Size Classical Guitar in White</t>
+        </is>
+      </c>
+      <c r="E237" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F237" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G237" s="16" t="inlineStr">
+        <is>
+          <t>03/10 09:45: General inquiry - provided assistance | Status: Order found</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B239" s="15" t="inlineStr">
+        <is>
+          <t>26-14298-78579</t>
+        </is>
+      </c>
+      <c r="C239" s="15" t="inlineStr">
+        <is>
+          <t>*S1044</t>
+        </is>
+      </c>
+      <c r="D239" s="16" t="inlineStr">
+        <is>
+          <t>Stentor Student I 4/4 Size Cello Outfit</t>
+        </is>
+      </c>
+      <c r="E239" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F239" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G239" s="16" t="inlineStr">
+        <is>
+          <t>03/10 09:53: General inquiry - provided assistance | Status: Order found</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="B241" s="15" t="inlineStr">
+        <is>
+          <t>26-14316-60714</t>
+        </is>
+      </c>
+      <c r="C241" s="15" t="inlineStr">
+        <is>
+          <t>*EP1301</t>
+        </is>
+      </c>
+      <c r="D241" s="16" t="inlineStr">
+        <is>
+          <t>DiMarzio Switchcraft 1/4" Guitar Output Jack Socket Mono Input EP1301</t>
+        </is>
+      </c>
+      <c r="E241" s="15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F241" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G241" s="16" t="inlineStr">
+        <is>
+          <t>on po</t>
         </is>
       </c>
     </row>
